--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -1,38 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4F9F5D-C519-420C-8A48-9590F5D954DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47250F02-F1DE-4BD7-A123-14BD76AECF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排产结果-生产计划排产结果" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$2:$BU$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$2:$BN$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
-  <si>
-    <t>工厂</t>
-  </si>
-  <si>
-    <t>年份</t>
-  </si>
-  <si>
-    <t>月份</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>计划类型</t>
   </si>
@@ -82,61 +73,6 @@
     <t>净需求</t>
   </si>
   <si>
-    <t>周期储备需求</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>实际生产需求</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>含损耗</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>【这一列隐藏掉，我们默认的就是奇数+3/偶数+2，不需要再单独呈现】</t>
-    </r>
-  </si>
-  <si>
     <t>生产实际排产量</t>
   </si>
   <si>
@@ -248,18 +184,6 @@
     <t>31号</t>
   </si>
   <si>
-    <t>合计排产</t>
-  </si>
-  <si>
-    <t>{.factoryCode}</t>
-  </si>
-  <si>
-    <t>{.year}</t>
-  </si>
-  <si>
-    <t>{.month}</t>
-  </si>
-  <si>
     <t>{.planType}</t>
   </si>
   <si>
@@ -396,103 +320,79 @@
   </si>
   <si>
     <t>{.conventionProductionQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.monthPlanVersion}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productionVersion}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.differenceQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.postponeProductionQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.midProductionQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.heightProductionQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.totalQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.prodReqPlan}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.dayVulcanizationQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.inventorySalesRatio}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.averageSaleQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.typeBlockQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.proSize}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.productStatus}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.embryoCode}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.mainMaterialDesc}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.constructionStage}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productTypeCode}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>中优先级净需求</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.midQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{.cycleReserveQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>需求计划版本</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品品类</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -508,31 +408,31 @@
       </rPr>
       <t>物料编码</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>示方书类型</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>排产类型</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>英寸</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>产品分类</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>高优先级净需求</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>未排产数量</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>上机日期</t>
@@ -541,43 +441,47 @@
     <t>收尾日期</t>
   </si>
   <si>
-    <t>备注</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>{.totalAll}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.remark}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>工厂：{factoryName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品品类：{productTypeCode}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>需求计划版本：{monthPlanVersion}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productCategory}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期储备需求</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计排产</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{factoryName}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>排产版本号:{productionVersion}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productCategory}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.structureType}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -596,20 +500,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -653,6 +543,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -674,7 +572,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -684,25 +582,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="23"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="23"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="23"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="23"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -712,45 +601,54 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1027,515 +925,458 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BU3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BN3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16.75" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="16.75" customWidth="1"/>
-    <col min="9" max="9" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="34.25" customWidth="1"/>
-    <col min="11" max="11" width="18.875" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.125" customWidth="1"/>
-    <col min="15" max="15" width="11.625" customWidth="1"/>
-    <col min="16" max="23" width="16.75" customWidth="1"/>
-    <col min="24" max="24" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="24.75" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="26.5" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.875" customWidth="1"/>
-    <col min="38" max="38" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="23.375" customWidth="1"/>
-    <col min="40" max="40" width="16.75" customWidth="1"/>
-    <col min="41" max="71" width="6.125" customWidth="1"/>
-    <col min="72" max="73" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="10.4140625" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14.75" customWidth="1"/>
+    <col min="4" max="4" width="34.25" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.58203125" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="37.33203125" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" customWidth="1"/>
+    <col min="11" max="14" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="9.83203125" customWidth="1"/>
+    <col min="16" max="18" width="6.1640625" customWidth="1"/>
+    <col min="19" max="23" width="8.1640625" customWidth="1"/>
+    <col min="24" max="24" width="7.83203125" customWidth="1"/>
+    <col min="25" max="25" width="7.1640625" customWidth="1"/>
+    <col min="26" max="26" width="7.5" customWidth="1"/>
+    <col min="27" max="27" width="7.1640625" customWidth="1"/>
+    <col min="28" max="28" width="7.75" customWidth="1"/>
+    <col min="29" max="31" width="7.1640625" customWidth="1"/>
+    <col min="32" max="32" width="8" customWidth="1"/>
+    <col min="33" max="34" width="7.1640625" customWidth="1"/>
+    <col min="35" max="65" width="6.1640625" customWidth="1"/>
+    <col min="66" max="66" width="11" customWidth="1"/>
+    <col min="67" max="70" width="6.08203125" customWidth="1"/>
+    <col min="71" max="72" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H1" s="11"/>
+    <row r="1" spans="1:66" s="8" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="9"/>
     </row>
-    <row r="2" spans="1:73" s="1" customFormat="1" ht="81.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:66" s="1" customFormat="1" ht="82" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y2" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="Z2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH2" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AQ2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AS2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AU2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AV2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AY2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AZ2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="BA2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="BB2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="BC2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="BD2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="BE2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="BF2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="BH2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="BI2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="BJ2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="BK2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="BL2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="BM2" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="BN2" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O2" s="10" t="s">
+    </row>
+    <row r="3" spans="1:66" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="U2" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB2" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="AC2" s="8" t="s">
+      <c r="G3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BN3" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL2" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="AM2" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN2" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AU2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AY2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="BA2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="BC2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="BF2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="BG2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="BI2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BJ2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="BK2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="BL2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="BM2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="BN2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="BO2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="BP2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="BQ2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="BR2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="BT2" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="BU2" s="10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:73" s="1" customFormat="1" ht="81.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="P3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>68</v>
-      </c>
-      <c r="R3" t="s">
-        <v>69</v>
-      </c>
-      <c r="S3" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="V3" t="s">
-        <v>71</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AF3" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG3" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH3" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AJ3" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="AK3" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AL3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>89</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>92</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>93</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>94</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>97</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>99</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>100</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>102</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>103</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>105</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>106</v>
-      </c>
-      <c r="BT3" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BU3" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState ref="A2:BU3">
-      <sortCondition descending="1" ref="AG2:AG3"/>
-    </sortState>
-  </autoFilter>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-  </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <autoFilter ref="A2:BN2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47250F02-F1DE-4BD7-A123-14BD76AECF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADE8C7F-32EF-4262-A14E-5882514CFF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,6 +404,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>物料编码</t>
@@ -501,6 +502,7 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -572,7 +574,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -580,50 +582,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -632,23 +607,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -956,421 +940,421 @@
     <col min="71" max="72" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" s="8" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:66" s="4" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="9"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:66" s="1" customFormat="1" ht="82" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="X2" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AA2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AB2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AE2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="AG2" s="11" t="s">
+      <c r="AG2" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AH2" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AI2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AJ2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AK2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AL2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AM2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AN2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AO2" s="10" t="s">
+      <c r="AO2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AP2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AQ2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AR2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AS2" s="10" t="s">
+      <c r="AS2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AT2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AU2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AV2" s="10" t="s">
+      <c r="AV2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AW2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AX2" s="10" t="s">
+      <c r="AX2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="AY2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AZ2" s="10" t="s">
+      <c r="AZ2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="BA2" s="10" t="s">
+      <c r="BA2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BB2" s="10" t="s">
+      <c r="BB2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BC2" s="10" t="s">
+      <c r="BC2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BD2" s="10" t="s">
+      <c r="BD2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BE2" s="10" t="s">
+      <c r="BE2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BF2" s="10" t="s">
+      <c r="BF2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BG2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BH2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BI2" s="10" t="s">
+      <c r="BI2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BK2" s="10" t="s">
+      <c r="BK2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BL2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BM2" s="10" t="s">
+      <c r="BM2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BN2" s="14" t="s">
+      <c r="BN2" s="10" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:66" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AC3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AG3" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AH3" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AI3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="AJ3" s="2" t="s">
+      <c r="AJ3" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AK3" s="2" t="s">
+      <c r="AK3" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="AL3" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="AN3" s="2" t="s">
+      <c r="AN3" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="AO3" s="2" t="s">
+      <c r="AO3" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AP3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AQ3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AR3" s="2" t="s">
+      <c r="AR3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AS3" s="2" t="s">
+      <c r="AS3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="AT3" s="2" t="s">
+      <c r="AT3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="AU3" s="2" t="s">
+      <c r="AU3" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="AV3" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AW3" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="AX3" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="AY3" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="AZ3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BA3" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="BB3" s="2" t="s">
+      <c r="BB3" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BC3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BD3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BE3" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BF3" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="BH3" s="2" t="s">
+      <c r="BH3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="BI3" s="2" t="s">
+      <c r="BI3" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="BJ3" s="2" t="s">
+      <c r="BJ3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BK3" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="BL3" s="2" t="s">
+      <c r="BL3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="BM3" s="2" t="s">
+      <c r="BM3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="BN3" s="6" t="s">
+      <c r="BN3" s="14" t="s">
         <v>126</v>
       </c>
     </row>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADE8C7F-32EF-4262-A14E-5882514CFF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82845FF5-445C-4B31-9CD7-BF7DB57C2BE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排产结果-生产计划排产结果" sheetId="1" r:id="rId1"/>
@@ -25,165 +25,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
-    <t>计划类型</t>
-  </si>
-  <si>
-    <t>物料编码</t>
-  </si>
-  <si>
-    <t>物料描述</t>
-  </si>
-  <si>
-    <t>产品结构</t>
-  </si>
-  <si>
-    <t>胎胚号</t>
-  </si>
-  <si>
-    <t>胎胚描述</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>规格</t>
-  </si>
-  <si>
-    <t>主花纹</t>
-  </si>
-  <si>
-    <t>花纹</t>
-  </si>
-  <si>
-    <t>型腔</t>
-  </si>
-  <si>
-    <t>活块</t>
-  </si>
-  <si>
-    <t>月均销量</t>
-  </si>
-  <si>
-    <t>库销比</t>
-  </si>
-  <si>
-    <t>日硫化量</t>
-  </si>
-  <si>
-    <t>净需求</t>
-  </si>
-  <si>
-    <t>生产实际排产量</t>
-  </si>
-  <si>
-    <t>高优先级排产数量</t>
-  </si>
-  <si>
-    <t>中优先级排产数量</t>
-  </si>
-  <si>
-    <t>周期排产储备排产数量</t>
-  </si>
-  <si>
-    <t>常规储备排产数量</t>
-  </si>
-  <si>
-    <t>暂缓订单排产数量</t>
-  </si>
-  <si>
-    <t>1号</t>
-  </si>
-  <si>
-    <t>2号</t>
-  </si>
-  <si>
-    <t>3号</t>
-  </si>
-  <si>
-    <t>4号</t>
-  </si>
-  <si>
-    <t>5号</t>
-  </si>
-  <si>
-    <t>6号</t>
-  </si>
-  <si>
-    <t>7号</t>
-  </si>
-  <si>
-    <t>8号</t>
-  </si>
-  <si>
-    <t>9号</t>
-  </si>
-  <si>
-    <t>10号</t>
-  </si>
-  <si>
-    <t>11号</t>
-  </si>
-  <si>
-    <t>12号</t>
-  </si>
-  <si>
-    <t>13号</t>
-  </si>
-  <si>
-    <t>14号</t>
-  </si>
-  <si>
-    <t>15号</t>
-  </si>
-  <si>
-    <t>16号</t>
-  </si>
-  <si>
-    <t>17号</t>
-  </si>
-  <si>
-    <t>18号</t>
-  </si>
-  <si>
-    <t>19号</t>
-  </si>
-  <si>
-    <t>20号</t>
-  </si>
-  <si>
-    <t>21号</t>
-  </si>
-  <si>
-    <t>22号</t>
-  </si>
-  <si>
-    <t>23号</t>
-  </si>
-  <si>
-    <t>24号</t>
-  </si>
-  <si>
-    <t>25号</t>
-  </si>
-  <si>
-    <t>26号</t>
-  </si>
-  <si>
-    <t>27号</t>
-  </si>
-  <si>
-    <t>28号</t>
-  </si>
-  <si>
-    <t>29号</t>
-  </si>
-  <si>
-    <t>30号</t>
-  </si>
-  <si>
-    <t>31号</t>
-  </si>
-  <si>
     <t>{.planType}</t>
   </si>
   <si>
@@ -320,79 +161,79 @@
   </si>
   <si>
     <t>{.conventionProductionQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.differenceQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.postponeProductionQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.midProductionQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.heightProductionQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.totalQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.prodReqPlan}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.dayVulcanizationQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.inventorySalesRatio}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.averageSaleQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.typeBlockQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.proSize}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.productStatus}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.embryoCode}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.mainMaterialDesc}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.constructionStage}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中优先级净需求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.midQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>{.cycleReserveQty}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -409,93 +250,300 @@
       </rPr>
       <t>物料编码</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>示方书类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>排产类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>英寸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>产品分类</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>高优先级净需求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>未排产数量</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.totalAll}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求计划版本：{monthPlanVersion}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productCategory}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期储备需求</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计排产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{factoryName}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>排产版本号:{productionVersion}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.structureType}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品结构</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胎胚号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>胎胚描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主花纹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花纹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>型腔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活块</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>月均销量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>库销比</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日硫化量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>净需求</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产实际排产量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高优先级排产数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中优先级排产数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期排产储备排产数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规储备排产数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂缓订单排产数量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>上机日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>收尾日期</t>
-  </si>
-  <si>
-    <t>{.totalAll}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>需求计划版本：{monthPlanVersion}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productCategory}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>周期储备需求</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计排产</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{factoryName}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号:{productionVersion}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.structureType}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>11号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>14号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>16号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>18号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>19号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>23号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>24号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>28号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>29号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>31号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -523,14 +571,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color indexed="9"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
       <family val="2"/>
@@ -553,6 +593,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -563,23 +611,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="23"/>
+        <fgColor theme="8" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
+        <fgColor rgb="FF008080"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -588,51 +651,39 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -910,46 +961,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.4140625" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="34.25" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.58203125" customWidth="1"/>
+    <col min="5" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="11.625" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="37.33203125" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625" customWidth="1"/>
-    <col min="11" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="9.83203125" customWidth="1"/>
-    <col min="16" max="18" width="6.1640625" customWidth="1"/>
-    <col min="19" max="23" width="8.1640625" customWidth="1"/>
-    <col min="24" max="24" width="7.83203125" customWidth="1"/>
-    <col min="25" max="25" width="7.1640625" customWidth="1"/>
+    <col min="9" max="9" width="37.375" customWidth="1"/>
+    <col min="10" max="10" width="8.125" customWidth="1"/>
+    <col min="11" max="14" width="12.625" customWidth="1"/>
+    <col min="15" max="15" width="9.875" customWidth="1"/>
+    <col min="16" max="18" width="6.125" customWidth="1"/>
+    <col min="19" max="23" width="8.125" customWidth="1"/>
+    <col min="24" max="24" width="7.875" customWidth="1"/>
+    <col min="25" max="25" width="7.125" customWidth="1"/>
     <col min="26" max="26" width="7.5" customWidth="1"/>
-    <col min="27" max="27" width="7.1640625" customWidth="1"/>
+    <col min="27" max="27" width="7.125" customWidth="1"/>
     <col min="28" max="28" width="7.75" customWidth="1"/>
-    <col min="29" max="31" width="7.1640625" customWidth="1"/>
+    <col min="29" max="31" width="7.125" customWidth="1"/>
     <col min="32" max="32" width="8" customWidth="1"/>
-    <col min="33" max="34" width="7.1640625" customWidth="1"/>
-    <col min="35" max="65" width="6.1640625" customWidth="1"/>
+    <col min="33" max="34" width="7.125" customWidth="1"/>
+    <col min="35" max="65" width="6.125" customWidth="1"/>
     <col min="66" max="66" width="11" customWidth="1"/>
-    <col min="67" max="70" width="6.08203125" customWidth="1"/>
+    <col min="67" max="70" width="6.125" customWidth="1"/>
     <col min="71" max="72" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" s="4" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:66" s="4" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="4" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -958,409 +1009,409 @@
       <c r="J1" s="3"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:66" s="1" customFormat="1" ht="82" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:66" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG2" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AK2" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AL2" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="AM2" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN2" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AO2" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AP2" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="AR2" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AS2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AT2" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AU2" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX2" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY2" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ2" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="BA2" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB2" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC2" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="BE2" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BF2" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="BG2" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH2" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="BI2" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="BJ2" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK2" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="BL2" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="BM2" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="BN2" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="F3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="X3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="AD3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="AH3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="AI3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="AJ3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="W2" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="X2" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y2" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z2" s="8" t="s">
+      <c r="AK3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AL3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AM3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AN3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AO3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AP3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AF2" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="AH2" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI2" s="6" t="s">
+      <c r="AQ3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AR3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AK2" s="6" t="s">
+      <c r="AS3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AL2" s="6" t="s">
+      <c r="AT3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AM2" s="6" t="s">
+      <c r="AU3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AN2" s="6" t="s">
+      <c r="AV3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AO2" s="6" t="s">
+      <c r="AW3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AP2" s="6" t="s">
+      <c r="AX3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AQ2" s="6" t="s">
+      <c r="AY3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AR2" s="6" t="s">
+      <c r="AZ3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AS2" s="6" t="s">
+      <c r="BA3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="BB3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AU2" s="6" t="s">
+      <c r="BC3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AV2" s="6" t="s">
+      <c r="BD3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AW2" s="6" t="s">
+      <c r="BE3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AX2" s="6" t="s">
+      <c r="BF3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AY2" s="6" t="s">
+      <c r="BG3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AZ2" s="6" t="s">
+      <c r="BH3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="BA2" s="6" t="s">
+      <c r="BI3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BB2" s="6" t="s">
+      <c r="BJ3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BK3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BL3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BE2" s="6" t="s">
+      <c r="BM3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BF2" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BG2" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="BH2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="BI2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="BJ2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="BK2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="BL2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="BM2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="BN2" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:66" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="R3" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="U3" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="W3" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="X3" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y3" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z3" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA3" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB3" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC3" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD3" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE3" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG3" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI3" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ3" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL3" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM3" s="11" t="s">
+      <c r="BN3" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="AN3" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="AO3" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AP3" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR3" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="AS3" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AU3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="AW3" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AX3" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AY3" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AZ3" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="BA3" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="BB3" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="BC3" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="BE3" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="BF3" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="BG3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="BH3" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="BI3" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="BJ3" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="BK3" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="BL3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="BM3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="BN3" s="14" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:BN2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82845FF5-445C-4B31-9CD7-BF7DB57C2BE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F32563-C723-4A73-8BF6-C23E63AACBC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排产结果-生产计划排产结果" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$2:$BN$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$3:$BN$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="201">
   <si>
     <t>{.planType}</t>
   </si>
@@ -532,12 +533,210 @@
     <t>31号</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>{.planTypeA}</t>
+  </si>
+  <si>
+    <t>{.materialCodeA}</t>
+  </si>
+  <si>
+    <t>{.mesMaterialCodeA}</t>
+  </si>
+  <si>
+    <t>{.materialDescA}</t>
+  </si>
+  <si>
+    <t>{.structureNameA}</t>
+  </si>
+  <si>
+    <t>{.structureTypeA}</t>
+  </si>
+  <si>
+    <t>{.productStatusA}</t>
+  </si>
+  <si>
+    <t>{.embryoCodeA}</t>
+  </si>
+  <si>
+    <t>{.mainMaterialDescA}</t>
+  </si>
+  <si>
+    <t>{.constructionStageA}</t>
+  </si>
+  <si>
+    <t>{.brandA}</t>
+  </si>
+  <si>
+    <t>{.specificationsA}</t>
+  </si>
+  <si>
+    <t>{.mainPatternA}</t>
+  </si>
+  <si>
+    <t>{.patternA}</t>
+  </si>
+  <si>
+    <t>{.proSizeA}</t>
+  </si>
+  <si>
+    <t>{.productCategoryA}</t>
+  </si>
+  <si>
+    <t>{.mouldCavityQtyA}</t>
+  </si>
+  <si>
+    <t>{.typeBlockQtyA}</t>
+  </si>
+  <si>
+    <t>{.averageSaleQtyA}</t>
+  </si>
+  <si>
+    <t>{.inventorySalesRatioA}</t>
+  </si>
+  <si>
+    <t>{.dayVulcanizationQtyA}</t>
+  </si>
+  <si>
+    <t>{.prodReqPlanA}</t>
+  </si>
+  <si>
+    <t>{.heightQtyA}</t>
+  </si>
+  <si>
+    <t>{.midQtyA}</t>
+  </si>
+  <si>
+    <t>{.cycleReserveQtyA}</t>
+  </si>
+  <si>
+    <t>{.totalQtyA}</t>
+  </si>
+  <si>
+    <t>{.heightProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.midProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.cycleProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.conventionProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.postponeProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.differenceQtyA}</t>
+  </si>
+  <si>
+    <t>{.beginDayA}</t>
+  </si>
+  <si>
+    <t>{.endDayA}</t>
+  </si>
+  <si>
+    <t>{.day1A}</t>
+  </si>
+  <si>
+    <t>{.day2A}</t>
+  </si>
+  <si>
+    <t>{.day3A}</t>
+  </si>
+  <si>
+    <t>{.day4A}</t>
+  </si>
+  <si>
+    <t>{.day5A}</t>
+  </si>
+  <si>
+    <t>{.day6A}</t>
+  </si>
+  <si>
+    <t>{.day7A}</t>
+  </si>
+  <si>
+    <t>{.day8A}</t>
+  </si>
+  <si>
+    <t>{.day9A}</t>
+  </si>
+  <si>
+    <t>{.day10A}</t>
+  </si>
+  <si>
+    <t>{.day11A}</t>
+  </si>
+  <si>
+    <t>{.day12A}</t>
+  </si>
+  <si>
+    <t>{.day13A}</t>
+  </si>
+  <si>
+    <t>{.day14A}</t>
+  </si>
+  <si>
+    <t>{.day15A}</t>
+  </si>
+  <si>
+    <t>{.day16A}</t>
+  </si>
+  <si>
+    <t>{.day17A}</t>
+  </si>
+  <si>
+    <t>{.day18A}</t>
+  </si>
+  <si>
+    <t>{.day19A}</t>
+  </si>
+  <si>
+    <t>{.day20A}</t>
+  </si>
+  <si>
+    <t>{.day21A}</t>
+  </si>
+  <si>
+    <t>{.day22A}</t>
+  </si>
+  <si>
+    <t>{.day23A}</t>
+  </si>
+  <si>
+    <t>{.day24A}</t>
+  </si>
+  <si>
+    <t>{.day25A}</t>
+  </si>
+  <si>
+    <t>{.day26A}</t>
+  </si>
+  <si>
+    <t>{.day27A}</t>
+  </si>
+  <si>
+    <t>{.day28A}</t>
+  </si>
+  <si>
+    <t>{.day29A}</t>
+  </si>
+  <si>
+    <t>{.day30A}</t>
+  </si>
+  <si>
+    <t>{.day31A}</t>
+  </si>
+  <si>
+    <t>{.totalAllA}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -601,8 +800,20 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -619,6 +830,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF008080"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
       </patternFill>
     </fill>
   </fills>
@@ -651,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -685,6 +901,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -960,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BN4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -1009,410 +1226,952 @@
       <c r="J1" s="3"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:66" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:66" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="U2" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="V2" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y2" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z2" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC2" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH2" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI2" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ2" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK2" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL2" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM2" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="AN2" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO2" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP2" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="AQ2" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR2" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="AS2" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="AT2" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="AU2" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV2" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="AW2" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="AX2" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="AY2" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="AZ2" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="BA2" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="BB2" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="BC2" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="BD2" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="BE2" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="BF2" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="BG2" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="BH2" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="BI2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="BJ2" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="BK2" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="BL2" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="BM2" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="BN2" s="11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B3" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N3" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O3" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P3" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R3" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S3" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T3" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U3" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V3" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="W3" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="X3" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="Z3" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AA3" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AB3" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC3" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD3" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AE3" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AF3" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="AG2" s="10" t="s">
+      <c r="AG3" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AH3" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AI3" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AJ3" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AK3" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AL3" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AM3" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AN3" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="AO2" s="10" t="s">
+      <c r="AO3" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AP3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AQ3" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AR3" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="AS2" s="10" t="s">
+      <c r="AS3" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AT3" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AU3" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="AV2" s="10" t="s">
+      <c r="AV3" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AW3" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="AX2" s="10" t="s">
+      <c r="AX3" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="AY3" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="AZ2" s="10" t="s">
+      <c r="AZ3" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="BA2" s="10" t="s">
+      <c r="BA3" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="BB2" s="10" t="s">
+      <c r="BB3" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="BC2" s="10" t="s">
+      <c r="BC3" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="BD2" s="10" t="s">
+      <c r="BD3" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="BE2" s="10" t="s">
+      <c r="BE3" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="BF2" s="10" t="s">
+      <c r="BF3" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BG3" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BH3" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="BI2" s="10" t="s">
+      <c r="BI3" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BJ3" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="BK2" s="10" t="s">
+      <c r="BK3" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BL3" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="BM2" s="10" t="s">
+      <c r="BM3" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BN3" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:66" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:66" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="X4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Y4" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="Z4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AB4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AD4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AE4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AF4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="AH3" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AI3" s="6" t="s">
+      <c r="AI4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="AJ3" s="6" t="s">
+      <c r="AJ4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AK3" s="6" t="s">
+      <c r="AK4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL3" s="6" t="s">
+      <c r="AL4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AM3" s="6" t="s">
+      <c r="AM4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AN3" s="6" t="s">
+      <c r="AN4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="AO3" s="6" t="s">
+      <c r="AO4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AP3" s="6" t="s">
+      <c r="AP4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AQ3" s="6" t="s">
+      <c r="AQ4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AR3" s="6" t="s">
+      <c r="AR4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="AS3" s="6" t="s">
+      <c r="AS4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AT3" s="6" t="s">
+      <c r="AT4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AU3" s="6" t="s">
+      <c r="AU4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AV3" s="6" t="s">
+      <c r="AV4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AW3" s="6" t="s">
+      <c r="AW4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AX3" s="6" t="s">
+      <c r="AX4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AY3" s="6" t="s">
+      <c r="AY4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AZ3" s="6" t="s">
+      <c r="AZ4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BA3" s="6" t="s">
+      <c r="BA4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BB3" s="6" t="s">
+      <c r="BB4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="BC3" s="6" t="s">
+      <c r="BC4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BD3" s="6" t="s">
+      <c r="BD4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BE3" s="6" t="s">
+      <c r="BE4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BF3" s="6" t="s">
+      <c r="BF4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BG3" s="6" t="s">
+      <c r="BG4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BH3" s="6" t="s">
+      <c r="BH4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="BI3" s="6" t="s">
+      <c r="BI4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BJ3" s="6" t="s">
+      <c r="BJ4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BK3" s="6" t="s">
+      <c r="BK4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BL3" s="6" t="s">
+      <c r="BL4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BM3" s="6" t="s">
+      <c r="BM4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BN3" s="9" t="s">
+      <c r="BN4" s="9" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BN2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:BN3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978697F2-7896-40CB-93EB-D95BB74D0035}">
+  <dimension ref="A1:A66"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\CODES\JY_APS\JY_APS_CODE\jy_aps_admin\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F32563-C723-4A73-8BF6-C23E63AACBC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE56D36D-7B77-4A2F-BC5D-C7D3665988D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排产结果-生产计划排产结果" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$3:$BN$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$4:$BN$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -803,6 +803,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -867,7 +868,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -886,16 +887,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1178,37 +1173,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.75" customWidth="1"/>
     <col min="4" max="4" width="34.25" customWidth="1"/>
-    <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.58203125" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="37.375" customWidth="1"/>
-    <col min="10" max="10" width="8.125" customWidth="1"/>
-    <col min="11" max="14" width="12.625" customWidth="1"/>
-    <col min="15" max="15" width="9.875" customWidth="1"/>
-    <col min="16" max="18" width="6.125" customWidth="1"/>
-    <col min="19" max="23" width="8.125" customWidth="1"/>
-    <col min="24" max="24" width="7.875" customWidth="1"/>
-    <col min="25" max="25" width="7.125" customWidth="1"/>
+    <col min="9" max="9" width="37.33203125" customWidth="1"/>
+    <col min="10" max="10" width="8.08203125" customWidth="1"/>
+    <col min="11" max="14" width="12.58203125" customWidth="1"/>
+    <col min="15" max="15" width="9.83203125" customWidth="1"/>
+    <col min="16" max="18" width="6.08203125" customWidth="1"/>
+    <col min="19" max="23" width="8.08203125" customWidth="1"/>
+    <col min="24" max="24" width="7.83203125" customWidth="1"/>
+    <col min="25" max="25" width="7.08203125" customWidth="1"/>
     <col min="26" max="26" width="7.5" customWidth="1"/>
-    <col min="27" max="27" width="7.125" customWidth="1"/>
+    <col min="27" max="27" width="7.08203125" customWidth="1"/>
     <col min="28" max="28" width="7.75" customWidth="1"/>
-    <col min="29" max="31" width="7.125" customWidth="1"/>
+    <col min="29" max="31" width="7.08203125" customWidth="1"/>
     <col min="32" max="32" width="8" customWidth="1"/>
-    <col min="33" max="34" width="7.125" customWidth="1"/>
-    <col min="35" max="65" width="6.125" customWidth="1"/>
+    <col min="33" max="34" width="7.08203125" customWidth="1"/>
+    <col min="35" max="65" width="6.08203125" customWidth="1"/>
     <col min="66" max="66" width="11" customWidth="1"/>
-    <col min="67" max="70" width="6.125" customWidth="1"/>
+    <col min="67" max="70" width="6.08203125" customWidth="1"/>
     <col min="71" max="72" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" s="4" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:66" s="4" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>76</v>
       </c>
@@ -1226,608 +1221,608 @@
       <c r="J1" s="3"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:66" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:66" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="R2" s="11" t="s">
+      <c r="R2" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="V2" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="W2" s="11" t="s">
+      <c r="W2" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="X2" s="11" t="s">
+      <c r="X2" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="Z2" s="11" t="s">
+      <c r="Z2" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AB2" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="AC2" s="11" t="s">
+      <c r="AC2" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="AD2" s="11" t="s">
+      <c r="AD2" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AE2" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="AG2" s="11" t="s">
+      <c r="AG2" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="AH2" s="11" t="s">
+      <c r="AH2" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AI2" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="AJ2" s="11" t="s">
+      <c r="AJ2" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AK2" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AL2" s="11" t="s">
+      <c r="AL2" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AM2" s="11" t="s">
+      <c r="AM2" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AN2" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="AO2" s="11" t="s">
+      <c r="AO2" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AP2" s="11" t="s">
+      <c r="AP2" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="AQ2" s="11" t="s">
+      <c r="AQ2" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="AR2" s="11" t="s">
+      <c r="AR2" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="AS2" s="11" t="s">
+      <c r="AS2" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="AT2" s="11" t="s">
+      <c r="AT2" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="AU2" s="11" t="s">
+      <c r="AU2" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="AV2" s="11" t="s">
+      <c r="AV2" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="AW2" s="11" t="s">
+      <c r="AW2" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="AX2" s="11" t="s">
+      <c r="AX2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="AY2" s="11" t="s">
+      <c r="AY2" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="AZ2" s="11" t="s">
+      <c r="AZ2" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BA2" s="11" t="s">
+      <c r="BA2" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BB2" s="11" t="s">
+      <c r="BB2" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="BC2" s="11" t="s">
+      <c r="BC2" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="BD2" s="11" t="s">
+      <c r="BD2" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="BE2" s="11" t="s">
+      <c r="BE2" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="BF2" s="11" t="s">
+      <c r="BF2" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="BG2" s="11" t="s">
+      <c r="BG2" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="BH2" s="11" t="s">
+      <c r="BH2" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="BI2" s="11" t="s">
+      <c r="BI2" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="BJ2" s="11" t="s">
+      <c r="BJ2" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="BK2" s="11" t="s">
+      <c r="BK2" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="BL2" s="11" t="s">
+      <c r="BL2" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="BM2" s="11" t="s">
+      <c r="BM2" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="BN2" s="11" t="s">
+      <c r="BN2" s="9" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:66" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:66" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="Q3" s="10" t="s">
+      <c r="Q3" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="R3" s="10" t="s">
+      <c r="R3" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="T3" s="10" t="s">
+      <c r="T3" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="V3" s="10" t="s">
+      <c r="V3" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="W3" s="10" t="s">
+      <c r="W3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="X3" s="10" t="s">
+      <c r="X3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="Y3" s="10" t="s">
+      <c r="Y3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" s="10" t="s">
+      <c r="Z3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="10" t="s">
+      <c r="AA3" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="AB3" s="10" t="s">
+      <c r="AB3" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="AC3" s="10" t="s">
+      <c r="AC3" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="AD3" s="10" t="s">
+      <c r="AD3" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="AE3" s="10" t="s">
+      <c r="AE3" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="AF3" s="10" t="s">
+      <c r="AF3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="AG3" s="10" t="s">
+      <c r="AG3" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="AH3" s="10" t="s">
+      <c r="AH3" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="AI3" s="10" t="s">
+      <c r="AI3" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="AJ3" s="10" t="s">
+      <c r="AJ3" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="AK3" s="10" t="s">
+      <c r="AK3" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="AL3" s="10" t="s">
+      <c r="AL3" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="AM3" s="10" t="s">
+      <c r="AM3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="AN3" s="10" t="s">
+      <c r="AN3" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="AO3" s="10" t="s">
+      <c r="AO3" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="AP3" s="10" t="s">
+      <c r="AP3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="AQ3" s="10" t="s">
+      <c r="AQ3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="AR3" s="10" t="s">
+      <c r="AR3" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="AS3" s="10" t="s">
+      <c r="AS3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="AT3" s="10" t="s">
+      <c r="AT3" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="AU3" s="10" t="s">
+      <c r="AU3" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="AV3" s="10" t="s">
+      <c r="AV3" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AW3" s="10" t="s">
+      <c r="AW3" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="AX3" s="10" t="s">
+      <c r="AX3" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="AY3" s="10" t="s">
+      <c r="AY3" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="AZ3" s="10" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="BA3" s="10" t="s">
+      <c r="BA3" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="BB3" s="10" t="s">
+      <c r="BB3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BC3" s="10" t="s">
+      <c r="BC3" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="BD3" s="10" t="s">
+      <c r="BD3" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="BE3" s="10" t="s">
+      <c r="BE3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="BF3" s="10" t="s">
+      <c r="BF3" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="BG3" s="10" t="s">
+      <c r="BG3" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="BH3" s="10" t="s">
+      <c r="BH3" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="BI3" s="10" t="s">
+      <c r="BI3" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="BJ3" s="10" t="s">
+      <c r="BJ3" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BK3" s="10" t="s">
+      <c r="BK3" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="BL3" s="10" t="s">
+      <c r="BL3" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="BM3" s="10" t="s">
+      <c r="BM3" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="BN3" s="10" t="s">
+      <c r="BN3" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:66" s="1" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:66" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="U4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="V4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" t="s">
         <v>10</v>
       </c>
-      <c r="X4" s="8" t="s">
+      <c r="X4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="Y4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="Z4" s="7" t="s">
+      <c r="Z4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="7" t="s">
+      <c r="AA4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AB4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AC4" t="s">
         <v>11</v>
       </c>
-      <c r="AD4" s="7" t="s">
+      <c r="AD4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="AE4" s="7" t="s">
+      <c r="AE4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AF4" s="7" t="s">
+      <c r="AF4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AG4" s="6" t="s">
+      <c r="AG4" t="s">
         <v>12</v>
       </c>
-      <c r="AH4" s="6" t="s">
+      <c r="AH4" t="s">
         <v>13</v>
       </c>
-      <c r="AI4" s="6" t="s">
+      <c r="AI4" t="s">
         <v>14</v>
       </c>
-      <c r="AJ4" s="6" t="s">
+      <c r="AJ4" t="s">
         <v>15</v>
       </c>
-      <c r="AK4" s="6" t="s">
+      <c r="AK4" t="s">
         <v>16</v>
       </c>
-      <c r="AL4" s="6" t="s">
+      <c r="AL4" t="s">
         <v>17</v>
       </c>
-      <c r="AM4" s="6" t="s">
+      <c r="AM4" t="s">
         <v>18</v>
       </c>
-      <c r="AN4" s="6" t="s">
+      <c r="AN4" t="s">
         <v>19</v>
       </c>
-      <c r="AO4" s="6" t="s">
+      <c r="AO4" t="s">
         <v>20</v>
       </c>
-      <c r="AP4" s="6" t="s">
+      <c r="AP4" t="s">
         <v>21</v>
       </c>
-      <c r="AQ4" s="6" t="s">
+      <c r="AQ4" t="s">
         <v>22</v>
       </c>
-      <c r="AR4" s="6" t="s">
+      <c r="AR4" t="s">
         <v>23</v>
       </c>
-      <c r="AS4" s="6" t="s">
+      <c r="AS4" t="s">
         <v>24</v>
       </c>
-      <c r="AT4" s="6" t="s">
+      <c r="AT4" t="s">
         <v>25</v>
       </c>
-      <c r="AU4" s="6" t="s">
+      <c r="AU4" t="s">
         <v>26</v>
       </c>
-      <c r="AV4" s="6" t="s">
+      <c r="AV4" t="s">
         <v>27</v>
       </c>
-      <c r="AW4" s="6" t="s">
+      <c r="AW4" t="s">
         <v>28</v>
       </c>
-      <c r="AX4" s="6" t="s">
+      <c r="AX4" t="s">
         <v>29</v>
       </c>
-      <c r="AY4" s="6" t="s">
+      <c r="AY4" t="s">
         <v>30</v>
       </c>
-      <c r="AZ4" s="6" t="s">
+      <c r="AZ4" t="s">
         <v>31</v>
       </c>
-      <c r="BA4" s="6" t="s">
+      <c r="BA4" t="s">
         <v>32</v>
       </c>
-      <c r="BB4" s="6" t="s">
+      <c r="BB4" t="s">
         <v>33</v>
       </c>
-      <c r="BC4" s="6" t="s">
+      <c r="BC4" t="s">
         <v>34</v>
       </c>
-      <c r="BD4" s="6" t="s">
+      <c r="BD4" t="s">
         <v>35</v>
       </c>
-      <c r="BE4" s="6" t="s">
+      <c r="BE4" t="s">
         <v>36</v>
       </c>
-      <c r="BF4" s="6" t="s">
+      <c r="BF4" t="s">
         <v>37</v>
       </c>
-      <c r="BG4" s="6" t="s">
+      <c r="BG4" t="s">
         <v>38</v>
       </c>
-      <c r="BH4" s="6" t="s">
+      <c r="BH4" t="s">
         <v>39</v>
       </c>
-      <c r="BI4" s="6" t="s">
+      <c r="BI4" t="s">
         <v>40</v>
       </c>
-      <c r="BJ4" s="6" t="s">
+      <c r="BJ4" t="s">
         <v>41</v>
       </c>
-      <c r="BK4" s="6" t="s">
+      <c r="BK4" t="s">
         <v>42</v>
       </c>
-      <c r="BL4" s="6" t="s">
+      <c r="BL4" t="s">
         <v>43</v>
       </c>
-      <c r="BM4" s="6" t="s">
+      <c r="BM4" t="s">
         <v>44</v>
       </c>
-      <c r="BN4" s="9" t="s">
+      <c r="BN4" s="7" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:BN3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BN4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1837,334 +1832,334 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978697F2-7896-40CB-93EB-D95BB74D0035}">
   <dimension ref="A1:A66"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>200</v>
       </c>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE56D36D-7B77-4A2F-BC5D-C7D3665988D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AEA108-31DA-451C-AE8B-67BECB0932E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="排产结果-生产计划排产结果" sheetId="1" r:id="rId1"/>
+    <sheet name="月计划" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'排产结果-生产计划排产结果'!$A$4:$BN$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BN$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -162,79 +162,557 @@
   </si>
   <si>
     <t>{.conventionProductionQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.differenceQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.postponeProductionQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.midProductionQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.heightProductionQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.totalQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.prodReqPlan}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.dayVulcanizationQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.inventorySalesRatio}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.averageSaleQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.typeBlockQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.proSize}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.productStatus}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.embryoCode}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.mainMaterialDesc}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.constructionStage}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>中优先级净需求</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.midQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{.cycleReserveQty}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示方书类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排产类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英寸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高优先级净需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.totalAll}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求计划版本：{monthPlanVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productCategory}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期储备需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计排产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{factoryName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排产版本号:{productionVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.structureType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计划类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胎胚号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胎胚描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主花纹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花纹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>型腔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月均销量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库销比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日硫化量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产实际排产量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高优先级排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中优先级排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期排产储备排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规储备排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂缓订单排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上机日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收尾日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.planTypeA}</t>
+  </si>
+  <si>
+    <t>{.materialCodeA}</t>
+  </si>
+  <si>
+    <t>{.mesMaterialCodeA}</t>
+  </si>
+  <si>
+    <t>{.materialDescA}</t>
+  </si>
+  <si>
+    <t>{.structureNameA}</t>
+  </si>
+  <si>
+    <t>{.structureTypeA}</t>
+  </si>
+  <si>
+    <t>{.productStatusA}</t>
+  </si>
+  <si>
+    <t>{.embryoCodeA}</t>
+  </si>
+  <si>
+    <t>{.mainMaterialDescA}</t>
+  </si>
+  <si>
+    <t>{.constructionStageA}</t>
+  </si>
+  <si>
+    <t>{.brandA}</t>
+  </si>
+  <si>
+    <t>{.specificationsA}</t>
+  </si>
+  <si>
+    <t>{.mainPatternA}</t>
+  </si>
+  <si>
+    <t>{.patternA}</t>
+  </si>
+  <si>
+    <t>{.proSizeA}</t>
+  </si>
+  <si>
+    <t>{.productCategoryA}</t>
+  </si>
+  <si>
+    <t>{.mouldCavityQtyA}</t>
+  </si>
+  <si>
+    <t>{.typeBlockQtyA}</t>
+  </si>
+  <si>
+    <t>{.averageSaleQtyA}</t>
+  </si>
+  <si>
+    <t>{.inventorySalesRatioA}</t>
+  </si>
+  <si>
+    <t>{.dayVulcanizationQtyA}</t>
+  </si>
+  <si>
+    <t>{.prodReqPlanA}</t>
+  </si>
+  <si>
+    <t>{.heightQtyA}</t>
+  </si>
+  <si>
+    <t>{.midQtyA}</t>
+  </si>
+  <si>
+    <t>{.cycleReserveQtyA}</t>
+  </si>
+  <si>
+    <t>{.totalQtyA}</t>
+  </si>
+  <si>
+    <t>{.heightProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.midProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.cycleProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.conventionProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.postponeProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.differenceQtyA}</t>
+  </si>
+  <si>
+    <t>{.beginDayA}</t>
+  </si>
+  <si>
+    <t>{.endDayA}</t>
+  </si>
+  <si>
+    <t>{.day1A}</t>
+  </si>
+  <si>
+    <t>{.day2A}</t>
+  </si>
+  <si>
+    <t>{.day3A}</t>
+  </si>
+  <si>
+    <t>{.day4A}</t>
+  </si>
+  <si>
+    <t>{.day5A}</t>
+  </si>
+  <si>
+    <t>{.day6A}</t>
+  </si>
+  <si>
+    <t>{.day7A}</t>
+  </si>
+  <si>
+    <t>{.day8A}</t>
+  </si>
+  <si>
+    <t>{.day9A}</t>
+  </si>
+  <si>
+    <t>{.day10A}</t>
+  </si>
+  <si>
+    <t>{.day11A}</t>
+  </si>
+  <si>
+    <t>{.day12A}</t>
+  </si>
+  <si>
+    <t>{.day13A}</t>
+  </si>
+  <si>
+    <t>{.day14A}</t>
+  </si>
+  <si>
+    <t>{.day15A}</t>
+  </si>
+  <si>
+    <t>{.day16A}</t>
+  </si>
+  <si>
+    <t>{.day17A}</t>
+  </si>
+  <si>
+    <t>{.day18A}</t>
+  </si>
+  <si>
+    <t>{.day19A}</t>
+  </si>
+  <si>
+    <t>{.day20A}</t>
+  </si>
+  <si>
+    <t>{.day21A}</t>
+  </si>
+  <si>
+    <t>{.day22A}</t>
+  </si>
+  <si>
+    <t>{.day23A}</t>
+  </si>
+  <si>
+    <t>{.day24A}</t>
+  </si>
+  <si>
+    <t>{.day25A}</t>
+  </si>
+  <si>
+    <t>{.day26A}</t>
+  </si>
+  <si>
+    <t>{.day27A}</t>
+  </si>
+  <si>
+    <t>{.day28A}</t>
+  </si>
+  <si>
+    <t>{.day29A}</t>
+  </si>
+  <si>
+    <t>{.day30A}</t>
+  </si>
+  <si>
+    <t>{.day31A}</t>
+  </si>
+  <si>
+    <t>{.totalAllA}</t>
   </si>
   <si>
     <r>
@@ -245,512 +723,27 @@
         <b/>
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
+        <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
+        <scheme val="minor"/>
       </rPr>
       <t>物料编码</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>示方书类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>英寸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高优先级净需求</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>未排产数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.totalAll}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>需求计划版本：{monthPlanVersion}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productCategory}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>周期储备需求</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计排产</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{factoryName}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号:{productionVersion}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.structureType}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>计划类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料编码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品结构</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胎胚号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胎胚描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>品牌</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>规格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>主花纹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>花纹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>型腔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>活块</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>月均销量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>库销比</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日硫化量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>净需求</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生产实际排产量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>高优先级排产数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中优先级排产数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>周期排产储备排产数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>常规储备排产数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>暂缓订单排产数量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>上机日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>收尾日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>6号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>7号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>8号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>9号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>12号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>13号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>14号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>16号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>17号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>19号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>20号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>21号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>22号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>23号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>24号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>25号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>26号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>27号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>28号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>29号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>30号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>31号</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.planTypeA}</t>
-  </si>
-  <si>
-    <t>{.materialCodeA}</t>
-  </si>
-  <si>
-    <t>{.mesMaterialCodeA}</t>
-  </si>
-  <si>
-    <t>{.materialDescA}</t>
-  </si>
-  <si>
-    <t>{.structureNameA}</t>
-  </si>
-  <si>
-    <t>{.structureTypeA}</t>
-  </si>
-  <si>
-    <t>{.productStatusA}</t>
-  </si>
-  <si>
-    <t>{.embryoCodeA}</t>
-  </si>
-  <si>
-    <t>{.mainMaterialDescA}</t>
-  </si>
-  <si>
-    <t>{.constructionStageA}</t>
-  </si>
-  <si>
-    <t>{.brandA}</t>
-  </si>
-  <si>
-    <t>{.specificationsA}</t>
-  </si>
-  <si>
-    <t>{.mainPatternA}</t>
-  </si>
-  <si>
-    <t>{.patternA}</t>
-  </si>
-  <si>
-    <t>{.proSizeA}</t>
-  </si>
-  <si>
-    <t>{.productCategoryA}</t>
-  </si>
-  <si>
-    <t>{.mouldCavityQtyA}</t>
-  </si>
-  <si>
-    <t>{.typeBlockQtyA}</t>
-  </si>
-  <si>
-    <t>{.averageSaleQtyA}</t>
-  </si>
-  <si>
-    <t>{.inventorySalesRatioA}</t>
-  </si>
-  <si>
-    <t>{.dayVulcanizationQtyA}</t>
-  </si>
-  <si>
-    <t>{.prodReqPlanA}</t>
-  </si>
-  <si>
-    <t>{.heightQtyA}</t>
-  </si>
-  <si>
-    <t>{.midQtyA}</t>
-  </si>
-  <si>
-    <t>{.cycleReserveQtyA}</t>
-  </si>
-  <si>
-    <t>{.totalQtyA}</t>
-  </si>
-  <si>
-    <t>{.heightProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.midProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.cycleProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.conventionProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.postponeProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.differenceQtyA}</t>
-  </si>
-  <si>
-    <t>{.beginDayA}</t>
-  </si>
-  <si>
-    <t>{.endDayA}</t>
-  </si>
-  <si>
-    <t>{.day1A}</t>
-  </si>
-  <si>
-    <t>{.day2A}</t>
-  </si>
-  <si>
-    <t>{.day3A}</t>
-  </si>
-  <si>
-    <t>{.day4A}</t>
-  </si>
-  <si>
-    <t>{.day5A}</t>
-  </si>
-  <si>
-    <t>{.day6A}</t>
-  </si>
-  <si>
-    <t>{.day7A}</t>
-  </si>
-  <si>
-    <t>{.day8A}</t>
-  </si>
-  <si>
-    <t>{.day9A}</t>
-  </si>
-  <si>
-    <t>{.day10A}</t>
-  </si>
-  <si>
-    <t>{.day11A}</t>
-  </si>
-  <si>
-    <t>{.day12A}</t>
-  </si>
-  <si>
-    <t>{.day13A}</t>
-  </si>
-  <si>
-    <t>{.day14A}</t>
-  </si>
-  <si>
-    <t>{.day15A}</t>
-  </si>
-  <si>
-    <t>{.day16A}</t>
-  </si>
-  <si>
-    <t>{.day17A}</t>
-  </si>
-  <si>
-    <t>{.day18A}</t>
-  </si>
-  <si>
-    <t>{.day19A}</t>
-  </si>
-  <si>
-    <t>{.day20A}</t>
-  </si>
-  <si>
-    <t>{.day21A}</t>
-  </si>
-  <si>
-    <t>{.day22A}</t>
-  </si>
-  <si>
-    <t>{.day23A}</t>
-  </si>
-  <si>
-    <t>{.day24A}</t>
-  </si>
-  <si>
-    <t>{.day25A}</t>
-  </si>
-  <si>
-    <t>{.day26A}</t>
-  </si>
-  <si>
-    <t>{.day27A}</t>
-  </si>
-  <si>
-    <t>{.day28A}</t>
-  </si>
-  <si>
-    <t>{.day29A}</t>
-  </si>
-  <si>
-    <t>{.day30A}</t>
-  </si>
-  <si>
-    <t>{.day31A}</t>
-  </si>
-  <si>
-    <t>{.totalAllA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -766,14 +759,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -793,14 +778,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
@@ -810,8 +787,28 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -875,28 +872,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1205,440 +1202,440 @@
   <sheetData>
     <row r="1" spans="1:66" s="4" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" s="3"/>
-      <c r="D1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>77</v>
-      </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:66" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="BF1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="BK1" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:66" s="4" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="O2" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="P2" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="Q2" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="R2" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S2" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="T2" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="U2" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="V2" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="W2" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="X2" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="Y2" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="Y2" s="9" t="s">
+      <c r="Z2" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="AA2" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AB2" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="AB2" s="9" t="s">
+      <c r="AC2" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="AC2" s="9" t="s">
+      <c r="AD2" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="AD2" s="9" t="s">
+      <c r="AE2" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="AE2" s="9" t="s">
+      <c r="AF2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AF2" s="9" t="s">
+      <c r="AG2" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="AG2" s="9" t="s">
+      <c r="AH2" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="AH2" s="9" t="s">
+      <c r="AI2" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="AI2" s="9" t="s">
+      <c r="AJ2" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="AJ2" s="9" t="s">
+      <c r="AK2" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="AK2" s="9" t="s">
+      <c r="AL2" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AL2" s="9" t="s">
+      <c r="AM2" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AM2" s="9" t="s">
+      <c r="AN2" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AN2" s="9" t="s">
+      <c r="AO2" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AO2" s="9" t="s">
+      <c r="AP2" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AQ2" s="9" t="s">
+      <c r="AR2" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AR2" s="9" t="s">
+      <c r="AS2" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AS2" s="9" t="s">
+      <c r="AT2" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="AT2" s="9" t="s">
+      <c r="AU2" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="AU2" s="9" t="s">
+      <c r="AV2" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="AV2" s="9" t="s">
+      <c r="AW2" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="AW2" s="9" t="s">
+      <c r="AX2" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="AX2" s="9" t="s">
+      <c r="AY2" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="AY2" s="9" t="s">
+      <c r="AZ2" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="AZ2" s="9" t="s">
+      <c r="BA2" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="BA2" s="9" t="s">
+      <c r="BB2" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="BB2" s="9" t="s">
+      <c r="BC2" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="BC2" s="9" t="s">
+      <c r="BD2" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="BD2" s="9" t="s">
+      <c r="BE2" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="BE2" s="9" t="s">
+      <c r="BF2" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="BF2" s="9" t="s">
+      <c r="BG2" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="BG2" s="9" t="s">
+      <c r="BH2" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="BH2" s="9" t="s">
+      <c r="BI2" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="BI2" s="9" t="s">
+      <c r="BJ2" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="BJ2" s="9" t="s">
+      <c r="BK2" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="BK2" s="9" t="s">
+      <c r="BL2" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="BL2" s="9" t="s">
+      <c r="BM2" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="BM2" s="9" t="s">
+      <c r="BN2" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="BN2" s="9" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:66" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="E3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="8" t="s">
+      <c r="P3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="O3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="P3" s="8" t="s">
+      <c r="R3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="W3" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>61</v>
       </c>
       <c r="Y3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AI3" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="AL3" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="AM3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AR3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AS3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AT3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU3" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AV3" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW3" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AX3" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AY3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AZ3" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="BA3" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="BB3" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="BC3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BE3" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF3" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="BG3" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="BH3" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BJ3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BK3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BL3" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="BM3" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Z3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD3" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE3" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="AH3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="AI3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AJ3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AK3" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="AL3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="AM3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AN3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AO3" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP3" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AQ3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="AR3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="AS3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AT3" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AU3" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="AV3" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="AX3" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="AY3" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="AZ3" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="BA3" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB3" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="BC3" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="BD3" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="BE3" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="BF3" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="BG3" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="BH3" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="BI3" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="BJ3" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="BK3" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="BL3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="BM3" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="BN3" s="8" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="4" spans="1:66" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>57</v>
@@ -1652,25 +1649,25 @@
       <c r="J4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="O4" s="4" t="s">
         <v>56</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q4" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="R4" s="4" t="s">
@@ -1688,7 +1685,7 @@
       <c r="V4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="W4" t="s">
+      <c r="W4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="X4" s="6" t="s">
@@ -1706,7 +1703,7 @@
       <c r="AB4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AC4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="AD4" s="4" t="s">
@@ -1718,112 +1715,112 @@
       <c r="AF4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AH4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AI4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AJ4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AK4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AL4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AM4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AN4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AO4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AP4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AQ4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AR4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AS4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AT4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AU4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AV4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AW4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AX4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AY4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BA4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BB4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BC4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BD4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BE4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BF4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BG4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BH4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BI4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BJ4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BK4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BL4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="BN4" s="7" t="s">
-        <v>71</v>
+      <c r="BN4" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:BN4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1836,336 +1833,336 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E254BA3-F204-4B76-BD74-2DF013C5C08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F6A036-B30A-47CA-BC8B-B1C17B6DCD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F6A036-B30A-47CA-BC8B-B1C17B6DCD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F55B327-E8E0-4124-AD67-BADB53281710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -270,504 +270,504 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>排产版本号:{productionVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.structureType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物料描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胎胚号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胎胚描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主花纹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花纹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>型腔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月均销量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库销比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日硫化量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产实际排产量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高优先级排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中优先级排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周期排产储备排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常规储备排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂缓订单排产数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上机日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收尾日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.materialCodeA}</t>
+  </si>
+  <si>
+    <t>{.mesMaterialCodeA}</t>
+  </si>
+  <si>
+    <t>{.materialDescA}</t>
+  </si>
+  <si>
+    <t>{.structureNameA}</t>
+  </si>
+  <si>
+    <t>{.structureTypeA}</t>
+  </si>
+  <si>
+    <t>{.productStatusA}</t>
+  </si>
+  <si>
+    <t>{.embryoCodeA}</t>
+  </si>
+  <si>
+    <t>{.mainMaterialDescA}</t>
+  </si>
+  <si>
+    <t>{.constructionStageA}</t>
+  </si>
+  <si>
+    <t>{.brandA}</t>
+  </si>
+  <si>
+    <t>{.specificationsA}</t>
+  </si>
+  <si>
+    <t>{.mainPatternA}</t>
+  </si>
+  <si>
+    <t>{.patternA}</t>
+  </si>
+  <si>
+    <t>{.proSizeA}</t>
+  </si>
+  <si>
+    <t>{.mouldCavityQtyA}</t>
+  </si>
+  <si>
+    <t>{.typeBlockQtyA}</t>
+  </si>
+  <si>
+    <t>{.averageSaleQtyA}</t>
+  </si>
+  <si>
+    <t>{.inventorySalesRatioA}</t>
+  </si>
+  <si>
+    <t>{.dayVulcanizationQtyA}</t>
+  </si>
+  <si>
+    <t>{.prodReqPlanA}</t>
+  </si>
+  <si>
+    <t>{.heightQtyA}</t>
+  </si>
+  <si>
+    <t>{.midQtyA}</t>
+  </si>
+  <si>
+    <t>{.cycleReserveQtyA}</t>
+  </si>
+  <si>
+    <t>{.totalQtyA}</t>
+  </si>
+  <si>
+    <t>{.heightProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.midProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.cycleProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.conventionProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.postponeProductionQtyA}</t>
+  </si>
+  <si>
+    <t>{.beginDayA}</t>
+  </si>
+  <si>
+    <t>{.endDayA}</t>
+  </si>
+  <si>
+    <t>{.day1A}</t>
+  </si>
+  <si>
+    <t>{.day2A}</t>
+  </si>
+  <si>
+    <t>{.day3A}</t>
+  </si>
+  <si>
+    <t>{.day4A}</t>
+  </si>
+  <si>
+    <t>{.day5A}</t>
+  </si>
+  <si>
+    <t>{.day6A}</t>
+  </si>
+  <si>
+    <t>{.day7A}</t>
+  </si>
+  <si>
+    <t>{.day8A}</t>
+  </si>
+  <si>
+    <t>{.day9A}</t>
+  </si>
+  <si>
+    <t>{.day10A}</t>
+  </si>
+  <si>
+    <t>{.day11A}</t>
+  </si>
+  <si>
+    <t>{.day12A}</t>
+  </si>
+  <si>
+    <t>{.day13A}</t>
+  </si>
+  <si>
+    <t>{.day14A}</t>
+  </si>
+  <si>
+    <t>{.day15A}</t>
+  </si>
+  <si>
+    <t>{.day16A}</t>
+  </si>
+  <si>
+    <t>{.day17A}</t>
+  </si>
+  <si>
+    <t>{.day18A}</t>
+  </si>
+  <si>
+    <t>{.day19A}</t>
+  </si>
+  <si>
+    <t>{.day20A}</t>
+  </si>
+  <si>
+    <t>{.day21A}</t>
+  </si>
+  <si>
+    <t>{.day22A}</t>
+  </si>
+  <si>
+    <t>{.day23A}</t>
+  </si>
+  <si>
+    <t>{.day24A}</t>
+  </si>
+  <si>
+    <t>{.day25A}</t>
+  </si>
+  <si>
+    <t>{.day26A}</t>
+  </si>
+  <si>
+    <t>{.day27A}</t>
+  </si>
+  <si>
+    <t>{.day28A}</t>
+  </si>
+  <si>
+    <t>{.day29A}</t>
+  </si>
+  <si>
+    <t>{.day30A}</t>
+  </si>
+  <si>
+    <t>{.day31A}</t>
+  </si>
+  <si>
+    <t>{.totalAllA}</t>
+  </si>
+  <si>
+    <t>MES物料编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内外销</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.locationTypeA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标准胎量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productCategoryA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.singleTireWeightA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.singleTireWeight}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.locationType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{summary}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.day1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay2A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay1A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实单未排产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.actualOrderUnproducedA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.actualOrderUnproduced}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.differenceQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{factoryName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号:{productionVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.structureType}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胎胚号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胎胚描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>规格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主花纹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>花纹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>型腔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>月均销量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>库销比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日硫化量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>净需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生产实际排产量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高优先级排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中优先级排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周期排产储备排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>常规储备排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暂缓订单排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上机日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收尾日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>21号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>22号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>27号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>28号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>29号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>31号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.materialCodeA}</t>
-  </si>
-  <si>
-    <t>{.mesMaterialCodeA}</t>
-  </si>
-  <si>
-    <t>{.materialDescA}</t>
-  </si>
-  <si>
-    <t>{.structureNameA}</t>
-  </si>
-  <si>
-    <t>{.structureTypeA}</t>
-  </si>
-  <si>
-    <t>{.productStatusA}</t>
-  </si>
-  <si>
-    <t>{.embryoCodeA}</t>
-  </si>
-  <si>
-    <t>{.mainMaterialDescA}</t>
-  </si>
-  <si>
-    <t>{.constructionStageA}</t>
-  </si>
-  <si>
-    <t>{.brandA}</t>
-  </si>
-  <si>
-    <t>{.specificationsA}</t>
-  </si>
-  <si>
-    <t>{.mainPatternA}</t>
-  </si>
-  <si>
-    <t>{.patternA}</t>
-  </si>
-  <si>
-    <t>{.proSizeA}</t>
-  </si>
-  <si>
-    <t>{.mouldCavityQtyA}</t>
-  </si>
-  <si>
-    <t>{.typeBlockQtyA}</t>
-  </si>
-  <si>
-    <t>{.averageSaleQtyA}</t>
-  </si>
-  <si>
-    <t>{.inventorySalesRatioA}</t>
-  </si>
-  <si>
-    <t>{.dayVulcanizationQtyA}</t>
-  </si>
-  <si>
-    <t>{.prodReqPlanA}</t>
-  </si>
-  <si>
-    <t>{.heightQtyA}</t>
-  </si>
-  <si>
-    <t>{.midQtyA}</t>
-  </si>
-  <si>
-    <t>{.cycleReserveQtyA}</t>
-  </si>
-  <si>
-    <t>{.totalQtyA}</t>
-  </si>
-  <si>
-    <t>{.heightProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.midProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.cycleProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.conventionProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.postponeProductionQtyA}</t>
-  </si>
-  <si>
-    <t>{.beginDayA}</t>
-  </si>
-  <si>
-    <t>{.endDayA}</t>
-  </si>
-  <si>
-    <t>{.day1A}</t>
-  </si>
-  <si>
-    <t>{.day2A}</t>
-  </si>
-  <si>
-    <t>{.day3A}</t>
-  </si>
-  <si>
-    <t>{.day4A}</t>
-  </si>
-  <si>
-    <t>{.day5A}</t>
-  </si>
-  <si>
-    <t>{.day6A}</t>
-  </si>
-  <si>
-    <t>{.day7A}</t>
-  </si>
-  <si>
-    <t>{.day8A}</t>
-  </si>
-  <si>
-    <t>{.day9A}</t>
-  </si>
-  <si>
-    <t>{.day10A}</t>
-  </si>
-  <si>
-    <t>{.day11A}</t>
-  </si>
-  <si>
-    <t>{.day12A}</t>
-  </si>
-  <si>
-    <t>{.day13A}</t>
-  </si>
-  <si>
-    <t>{.day14A}</t>
-  </si>
-  <si>
-    <t>{.day15A}</t>
-  </si>
-  <si>
-    <t>{.day16A}</t>
-  </si>
-  <si>
-    <t>{.day17A}</t>
-  </si>
-  <si>
-    <t>{.day18A}</t>
-  </si>
-  <si>
-    <t>{.day19A}</t>
-  </si>
-  <si>
-    <t>{.day20A}</t>
-  </si>
-  <si>
-    <t>{.day21A}</t>
-  </si>
-  <si>
-    <t>{.day22A}</t>
-  </si>
-  <si>
-    <t>{.day23A}</t>
-  </si>
-  <si>
-    <t>{.day24A}</t>
-  </si>
-  <si>
-    <t>{.day25A}</t>
-  </si>
-  <si>
-    <t>{.day26A}</t>
-  </si>
-  <si>
-    <t>{.day27A}</t>
-  </si>
-  <si>
-    <t>{.day28A}</t>
-  </si>
-  <si>
-    <t>{.day29A}</t>
-  </si>
-  <si>
-    <t>{.day30A}</t>
-  </si>
-  <si>
-    <t>{.day31A}</t>
-  </si>
-  <si>
-    <t>{.totalAllA}</t>
-  </si>
-  <si>
-    <t>MES物料编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内外销</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.locationTypeA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标准胎量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productCategoryA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.singleTireWeightA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.singleTireWeight}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.locationType}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{summary}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{lastDay2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{lastDay1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.day1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay2A}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay1A}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实单未排产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproducedA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproduced}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.differenceQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -900,9 +900,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,10 +912,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1197,39 +1197,35 @@
   <dimension ref="A1:BR4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="34.25" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.58203125" customWidth="1"/>
-    <col min="7" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="37.33203125" customWidth="1"/>
-    <col min="10" max="10" width="8.08203125" customWidth="1"/>
-    <col min="11" max="14" width="12.58203125" customWidth="1"/>
-    <col min="15" max="16" width="9.83203125" customWidth="1"/>
-    <col min="17" max="19" width="6.08203125" customWidth="1"/>
-    <col min="20" max="24" width="8.08203125" customWidth="1"/>
-    <col min="25" max="25" width="7.83203125" customWidth="1"/>
-    <col min="26" max="26" width="7.08203125" customWidth="1"/>
-    <col min="27" max="27" width="7.5" customWidth="1"/>
-    <col min="28" max="28" width="7.08203125" customWidth="1"/>
-    <col min="29" max="29" width="7.75" customWidth="1"/>
-    <col min="30" max="32" width="7.08203125" customWidth="1"/>
-    <col min="33" max="34" width="8" customWidth="1"/>
-    <col min="35" max="36" width="7.08203125" customWidth="1"/>
-    <col min="37" max="69" width="6.08203125" customWidth="1"/>
-    <col min="70" max="70" width="11" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="3" width="7.9140625" customWidth="1"/>
+    <col min="4" max="4" width="33.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="6" max="7" width="9.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="30.5" customWidth="1"/>
+    <col min="10" max="10" width="5.1640625" customWidth="1"/>
+    <col min="11" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="15" width="9.08203125" customWidth="1"/>
+    <col min="16" max="16" width="4.58203125" customWidth="1"/>
+    <col min="17" max="17" width="7.83203125" customWidth="1"/>
+    <col min="18" max="19" width="5.4140625" customWidth="1"/>
+    <col min="20" max="20" width="5.9140625" customWidth="1"/>
+    <col min="21" max="23" width="5.75" customWidth="1"/>
+    <col min="24" max="32" width="6.33203125" customWidth="1"/>
+    <col min="33" max="33" width="8" customWidth="1"/>
+    <col min="34" max="35" width="7.08203125" customWidth="1"/>
+    <col min="36" max="69" width="6.08203125" customWidth="1"/>
+    <col min="70" max="70" width="8.4140625" customWidth="1"/>
     <col min="71" max="74" width="6.08203125" customWidth="1"/>
     <col min="75" max="76" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:70" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="A1" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="4"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -1238,7 +1234,7 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
-      <c r="K1" s="5"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -1265,7 +1261,7 @@
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
@@ -1299,293 +1295,293 @@
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
       <c r="BO1" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="BP1" s="3"/>
       <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
     </row>
     <row r="2" spans="1:70" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="A2" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="L2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="M2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="N2" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="O2" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="P2" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="R2" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="P2" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="R2" s="10" t="s">
+      <c r="S2" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="T2" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="U2" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="V2" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="W2" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="X2" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="Y2" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Z2" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="AA2" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AB2" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AC2" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AD2" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AE2" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="AE2" s="10" t="s">
+      <c r="AF2" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AG2" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="AI2" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="AG2" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AH2" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI2" s="10" t="s">
+      <c r="AJ2" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="AJ2" s="10" t="s">
+      <c r="AK2" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL2" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM2" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="AK2" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL2" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AN2" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AO2" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="AO2" s="10" t="s">
+      <c r="AP2" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AQ2" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="AQ2" s="10" t="s">
+      <c r="AR2" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="AR2" s="10" t="s">
+      <c r="AS2" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="AS2" s="10" t="s">
+      <c r="AT2" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="AT2" s="10" t="s">
+      <c r="AU2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AV2" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="AV2" s="10" t="s">
+      <c r="AW2" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="AW2" s="10" t="s">
+      <c r="AX2" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="AX2" s="10" t="s">
+      <c r="AY2" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="AZ2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="AZ2" s="10" t="s">
+      <c r="BA2" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="BA2" s="10" t="s">
+      <c r="BB2" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="BB2" s="10" t="s">
+      <c r="BC2" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="BC2" s="10" t="s">
+      <c r="BD2" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="BD2" s="10" t="s">
+      <c r="BE2" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="BE2" s="10" t="s">
+      <c r="BF2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="BF2" s="10" t="s">
+      <c r="BG2" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="BG2" s="10" t="s">
+      <c r="BH2" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="BH2" s="10" t="s">
+      <c r="BI2" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="BI2" s="10" t="s">
+      <c r="BJ2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="BJ2" s="10" t="s">
+      <c r="BK2" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="BK2" s="10" t="s">
+      <c r="BL2" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="BL2" s="10" t="s">
+      <c r="BM2" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="BM2" s="10" t="s">
+      <c r="BN2" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="BN2" s="10" t="s">
+      <c r="BO2" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="BO2" s="10" t="s">
+      <c r="BP2" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="BP2" s="10" t="s">
+      <c r="BQ2" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="BQ2" s="10" t="s">
+      <c r="BR2" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="BR2" s="10" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:70" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>61</v>
       </c>
       <c r="H3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>62</v>
       </c>
       <c r="K3" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="N3" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="O3" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q3" s="9" t="s">
         <v>64</v>
       </c>
       <c r="R3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="S3" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="T3" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="W3" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="X3" s="9" t="s">
         <v>65</v>
@@ -1597,347 +1593,347 @@
         <v>70</v>
       </c>
       <c r="AA3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB3" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AC3" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AD3" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AE3" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AF3" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="AF3" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="AG3" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH3" s="9" t="s">
         <v>66</v>
       </c>
       <c r="AI3" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="AJ3" s="9" t="s">
+      <c r="AK3" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="AM3" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="AK3" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AL3" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="AM3" s="9" t="s">
+      <c r="AN3" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AN3" s="9" t="s">
+      <c r="AO3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AO3" s="9" t="s">
+      <c r="AP3" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="AP3" s="9" t="s">
+      <c r="AQ3" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="AQ3" s="9" t="s">
+      <c r="AR3" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="AR3" s="9" t="s">
+      <c r="AS3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AS3" s="9" t="s">
+      <c r="AT3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="AT3" s="9" t="s">
+      <c r="AU3" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AU3" s="9" t="s">
+      <c r="AV3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="AV3" s="9" t="s">
+      <c r="AW3" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="AW3" s="9" t="s">
+      <c r="AX3" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="AX3" s="9" t="s">
+      <c r="AY3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="AY3" s="9" t="s">
+      <c r="AZ3" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="AZ3" s="9" t="s">
+      <c r="BA3" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="BA3" s="9" t="s">
+      <c r="BB3" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="BB3" s="9" t="s">
+      <c r="BC3" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="BC3" s="9" t="s">
+      <c r="BD3" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="BD3" s="9" t="s">
+      <c r="BE3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="BE3" s="9" t="s">
+      <c r="BF3" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="BF3" s="9" t="s">
+      <c r="BG3" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="BG3" s="9" t="s">
+      <c r="BH3" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="BH3" s="9" t="s">
+      <c r="BI3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="BI3" s="9" t="s">
+      <c r="BJ3" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="BJ3" s="9" t="s">
+      <c r="BK3" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="BK3" s="9" t="s">
+      <c r="BL3" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="BL3" s="9" t="s">
+      <c r="BM3" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="BM3" s="9" t="s">
+      <c r="BN3" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="BN3" s="9" t="s">
+      <c r="BO3" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="BO3" s="9" t="s">
+      <c r="BP3" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="BP3" s="9" t="s">
+      <c r="BQ3" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="BQ3" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="BR3" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:70" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q4" s="6" t="s">
+      <c r="P4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="X4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="Y4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="Z4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AA4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AB4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AC4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AD4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AE4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AF4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AG4" s="6" t="s">
+      <c r="AG4" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AH4" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="AH4" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI4" s="6" t="s">
+      <c r="AI4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AJ4" s="6" t="s">
+      <c r="AJ4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL4" s="6" t="s">
+      <c r="AK4" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="AM4" s="6" t="s">
+      <c r="AL4" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="AN4" s="6" t="s">
+      <c r="AM4" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="AN4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AO4" s="6" t="s">
+      <c r="AO4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AP4" s="6" t="s">
+      <c r="AP4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AQ4" s="6" t="s">
+      <c r="AQ4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="AR4" s="6" t="s">
+      <c r="AR4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AS4" s="6" t="s">
+      <c r="AS4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AT4" s="6" t="s">
+      <c r="AT4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AU4" s="6" t="s">
+      <c r="AU4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AV4" s="6" t="s">
+      <c r="AV4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AW4" s="6" t="s">
+      <c r="AW4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AX4" s="6" t="s">
+      <c r="AX4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AY4" s="6" t="s">
+      <c r="AY4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AZ4" s="6" t="s">
+      <c r="AZ4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="BA4" s="6" t="s">
+      <c r="BA4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="BB4" s="6" t="s">
+      <c r="BB4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="BC4" s="6" t="s">
+      <c r="BC4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="BD4" s="6" t="s">
+      <c r="BD4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="BE4" s="6" t="s">
+      <c r="BE4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="BF4" s="6" t="s">
+      <c r="BF4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="BG4" s="6" t="s">
+      <c r="BG4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="BH4" s="6" t="s">
+      <c r="BH4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="BI4" s="6" t="s">
+      <c r="BI4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="BJ4" s="6" t="s">
+      <c r="BJ4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="BK4" s="6" t="s">
+      <c r="BK4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="BL4" s="6" t="s">
+      <c r="BL4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="BM4" s="6" t="s">
+      <c r="BM4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="BN4" s="6" t="s">
+      <c r="BN4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="BO4" s="6" t="s">
+      <c r="BO4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="BP4" s="6" t="s">
+      <c r="BP4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="BQ4" s="6" t="s">
+      <c r="BQ4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="BR4" s="8" t="s">
+      <c r="BR4" s="7" t="s">
         <v>67</v>
       </c>
     </row>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F55B327-E8E0-4124-AD67-BADB53281710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33493D7-238B-49F0-AAFA-098BCD407C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -214,10 +214,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中优先级净需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.midQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -226,278 +222,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>示方书类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英寸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高优先级净需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.totalAll}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需求计划版本：{monthPlanVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.productCategory}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周期储备需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计排产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号:{productionVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结构类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.structureType}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>物料编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>物料描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胎胚号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胎胚描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品牌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>规格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主花纹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>花纹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>型腔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>月均销量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>库销比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日硫化量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>净需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生产实际排产量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高优先级排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中优先级排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周期排产储备排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>常规储备排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暂缓订单排产数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>上机日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收尾日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>19号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>21号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>22号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>25号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>27号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>28号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>29号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>31号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.materialCodeA}</t>
   </si>
   <si>
@@ -687,22 +423,10 @@
     <t>{.totalAllA}</t>
   </si>
   <si>
-    <t>MES物料编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内外销</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.locationTypeA}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>标准胎量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{.productCategoryA}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -723,51 +447,258 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{.day1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay2A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay1A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.actualOrderUnproducedA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.actualOrderUnproduced}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.differenceQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{factoryName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{locationType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{materialCode}</t>
+  </si>
+  <si>
+    <t>{mesMaterialCode}</t>
+  </si>
+  <si>
+    <t>{materialDesc}</t>
+  </si>
+  <si>
+    <t>{structureName}</t>
+  </si>
+  <si>
+    <t>{structureType}</t>
+  </si>
+  <si>
+    <t>{productStatus}</t>
+  </si>
+  <si>
+    <t>{embryoCode}</t>
+  </si>
+  <si>
+    <t>{mainMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{constructionStage}</t>
+  </si>
+  <si>
+    <t>{brand}</t>
+  </si>
+  <si>
+    <t>{specifications}</t>
+  </si>
+  <si>
+    <t>{mainPattern}</t>
+  </si>
+  <si>
+    <t>{pattern}</t>
+  </si>
+  <si>
+    <t>{proSize}</t>
+  </si>
+  <si>
+    <t>{singleTireWeight}</t>
+  </si>
+  <si>
+    <t>{productCategory}</t>
+  </si>
+  <si>
+    <t>{mouldCavityQty}</t>
+  </si>
+  <si>
+    <t>{typeBlockQty}</t>
+  </si>
+  <si>
+    <t>{averageSaleQty}</t>
+  </si>
+  <si>
+    <t>{inventorySalesRatio}</t>
+  </si>
+  <si>
+    <t>{dayVulcanizationQty}</t>
+  </si>
+  <si>
+    <t>{prodReqPlan}</t>
+  </si>
+  <si>
+    <t>{heightQty}</t>
+  </si>
+  <si>
+    <t>{midQty}</t>
+  </si>
+  <si>
+    <t>{cycleReserveQty}</t>
+  </si>
+  <si>
+    <t>{totalQty}</t>
+  </si>
+  <si>
+    <t>{heightProductionQty}</t>
+  </si>
+  <si>
+    <t>{midProductionQty}</t>
+  </si>
+  <si>
+    <t>{cycleProductionQty}</t>
+  </si>
+  <si>
+    <t>{conventionProductionQty}</t>
+  </si>
+  <si>
+    <t>{postponeProductionQty}</t>
+  </si>
+  <si>
+    <t>{actualOrderUnproduced}</t>
+  </si>
+  <si>
+    <t>{differenceQty}</t>
+  </si>
+  <si>
+    <t>{beginDay}</t>
+  </si>
+  <si>
+    <t>{endDay}</t>
+  </si>
+  <si>
     <t>{lastDay2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{lastDay1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.day1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay2A}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay1A}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实单未排产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproducedA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproduced}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.differenceQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{factoryName}</t>
+  </si>
+  <si>
+    <t>{day1}</t>
+  </si>
+  <si>
+    <t>{day2}</t>
+  </si>
+  <si>
+    <t>{day3}</t>
+  </si>
+  <si>
+    <t>{day4}</t>
+  </si>
+  <si>
+    <t>{day5}</t>
+  </si>
+  <si>
+    <t>{day6}</t>
+  </si>
+  <si>
+    <t>{day7}</t>
+  </si>
+  <si>
+    <t>{day8}</t>
+  </si>
+  <si>
+    <t>{day9}</t>
+  </si>
+  <si>
+    <t>{day10}</t>
+  </si>
+  <si>
+    <t>{day11}</t>
+  </si>
+  <si>
+    <t>{day12}</t>
+  </si>
+  <si>
+    <t>{day13}</t>
+  </si>
+  <si>
+    <t>{day14}</t>
+  </si>
+  <si>
+    <t>{day15}</t>
+  </si>
+  <si>
+    <t>{day16}</t>
+  </si>
+  <si>
+    <t>{day17}</t>
+  </si>
+  <si>
+    <t>{day18}</t>
+  </si>
+  <si>
+    <t>{day19}</t>
+  </si>
+  <si>
+    <t>{day20}</t>
+  </si>
+  <si>
+    <t>{day21}</t>
+  </si>
+  <si>
+    <t>{day22}</t>
+  </si>
+  <si>
+    <t>{day23}</t>
+  </si>
+  <si>
+    <t>{day24}</t>
+  </si>
+  <si>
+    <t>{day25}</t>
+  </si>
+  <si>
+    <t>{day26}</t>
+  </si>
+  <si>
+    <t>{day27}</t>
+  </si>
+  <si>
+    <t>{day28}</t>
+  </si>
+  <si>
+    <t>{day29}</t>
+  </si>
+  <si>
+    <t>{day30}</t>
+  </si>
+  <si>
+    <t>{day31}</t>
+  </si>
+  <si>
+    <t>{totalAll}</t>
+  </si>
+  <si>
+    <t>{monthPlanVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{productionVersion}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1214,8 +1145,8 @@
     <col min="21" max="23" width="5.75" customWidth="1"/>
     <col min="24" max="32" width="6.33203125" customWidth="1"/>
     <col min="33" max="33" width="8" customWidth="1"/>
-    <col min="34" max="35" width="7.08203125" customWidth="1"/>
-    <col min="36" max="69" width="6.08203125" customWidth="1"/>
+    <col min="34" max="34" width="7.08203125" customWidth="1"/>
+    <col min="35" max="69" width="6.08203125" customWidth="1"/>
     <col min="70" max="70" width="8.4140625" customWidth="1"/>
     <col min="71" max="74" width="6.08203125" customWidth="1"/>
     <col min="75" max="76" width="16.75" customWidth="1"/>
@@ -1223,7 +1154,7 @@
   <sheetData>
     <row r="1" spans="1:70" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3"/>
@@ -1261,7 +1192,7 @@
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3" t="s">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
@@ -1288,14 +1219,14 @@
       <c r="BH1" s="3"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="3" t="s">
-        <v>68</v>
+        <v>211</v>
       </c>
       <c r="BK1" s="3"/>
       <c r="BL1" s="3"/>
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
       <c r="BO1" s="3" t="s">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="BP1" s="3"/>
       <c r="BQ1" s="3"/>
@@ -1303,431 +1234,431 @@
     </row>
     <row r="2" spans="1:70" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ2" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK2" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="AL2" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="AH2" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="AI2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="AJ2" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="AK2" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL2" s="8" t="s">
-        <v>207</v>
-      </c>
       <c r="AM2" s="8" t="s">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="AN2" s="8" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="AP2" s="8" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="AQ2" s="8" t="s">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="AR2" s="8" t="s">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="AS2" s="8" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="AT2" s="8" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="AU2" s="8" t="s">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="AV2" s="8" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="AW2" s="8" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="AX2" s="8" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="AY2" s="8" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="BA2" s="8" t="s">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="BB2" s="8" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="BC2" s="8" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="BD2" s="8" t="s">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="BE2" s="8" t="s">
-        <v>178</v>
+        <v>112</v>
       </c>
       <c r="BF2" s="8" t="s">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="BG2" s="8" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="BH2" s="8" t="s">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="BI2" s="8" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
       <c r="BJ2" s="8" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="BK2" s="8" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="BL2" s="8" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="BM2" s="8" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="BO2" s="8" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="BP2" s="8" t="s">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="BQ2" s="8" t="s">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="BR2" s="8" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:70" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE3" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP3" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="AR3" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="AS3" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="AT3" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="AU3" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AV3" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="AW3" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="AX3" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="AY3" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="AZ3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="BA3" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P3" s="9" t="s">
+      <c r="BB3" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="BC3" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="Q3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="S3" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z3" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB3" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD3" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="AE3" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AF3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG3" s="9" t="s">
+      <c r="BD3" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="BE3" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="BF3" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="BG3" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="BH3" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="BI3" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="BJ3" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="BK3" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="BL3" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="BM3" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="BN3" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="BO3" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="BP3" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="AH3" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI3" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ3" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK3" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL3" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AM3" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="AN3" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="AP3" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ3" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR3" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="AS3" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="AT3" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU3" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV3" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW3" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AX3" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="AY3" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ3" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="BA3" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="BB3" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="BC3" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="BD3" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="BE3" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="BF3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="BG3" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="BI3" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="BK3" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="BL3" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="BM3" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="BN3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="BO3" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="BP3" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="BQ3" s="9" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="BR3" s="9" t="s">
-        <v>71</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:70" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>199</v>
+        <v>130</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>0</v>
@@ -1742,7 +1673,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>54</v>
@@ -1772,10 +1703,10 @@
         <v>53</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>8</v>
@@ -1799,10 +1730,10 @@
         <v>9</v>
       </c>
       <c r="Y4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z4" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="AA4" s="5" t="s">
         <v>47</v>
@@ -1823,10 +1754,10 @@
         <v>44</v>
       </c>
       <c r="AG4" s="5" t="s">
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="AH4" s="5" t="s">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="AI4" s="5" t="s">
         <v>11</v>
@@ -1835,13 +1766,13 @@
         <v>12</v>
       </c>
       <c r="AK4" s="5" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="AM4" s="5" t="s">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="AN4" s="5" t="s">
         <v>13</v>
@@ -1934,7 +1865,7 @@
         <v>42</v>
       </c>
       <c r="BR4" s="7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33493D7-238B-49F0-AAFA-098BCD407C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAD3628-68CC-4843-92C0-AD06134E6697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -840,15 +840,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1153,7 +1153,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>140</v>
       </c>
       <c r="B1" s="4"/>
@@ -1233,426 +1233,426 @@
       <c r="BR1" s="3"/>
     </row>
     <row r="2" spans="1:70" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="U2" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="V2" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Y2" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="Z2" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AA2" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AB2" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AC2" s="8" t="s">
+      <c r="AC2" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AD2" s="8" t="s">
+      <c r="AD2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AE2" s="8" t="s">
+      <c r="AE2" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AF2" s="8" t="s">
+      <c r="AF2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AG2" s="8" t="s">
+      <c r="AG2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AH2" s="8" t="s">
+      <c r="AH2" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="AI2" s="8" t="s">
+      <c r="AI2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AJ2" s="8" t="s">
+      <c r="AJ2" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="AK2" s="8" t="s">
+      <c r="AK2" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="AL2" s="8" t="s">
+      <c r="AL2" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="AM2" s="8" t="s">
+      <c r="AM2" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="AN2" s="8" t="s">
+      <c r="AN2" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="AO2" s="8" t="s">
+      <c r="AO2" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AP2" s="8" t="s">
+      <c r="AP2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AQ2" s="8" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AR2" s="8" t="s">
+      <c r="AR2" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AS2" s="8" t="s">
+      <c r="AS2" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="AT2" s="8" t="s">
+      <c r="AT2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="AU2" s="8" t="s">
+      <c r="AU2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AV2" s="8" t="s">
+      <c r="AV2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AW2" s="8" t="s">
+      <c r="AW2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AX2" s="8" t="s">
+      <c r="AX2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AY2" s="8" t="s">
+      <c r="AY2" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="AZ2" s="8" t="s">
+      <c r="AZ2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="BA2" s="8" t="s">
+      <c r="BA2" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="BB2" s="8" t="s">
+      <c r="BB2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="BC2" s="8" t="s">
+      <c r="BC2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="BD2" s="8" t="s">
+      <c r="BD2" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="BE2" s="8" t="s">
+      <c r="BE2" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="BF2" s="8" t="s">
+      <c r="BF2" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="BG2" s="8" t="s">
+      <c r="BG2" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="BH2" s="8" t="s">
+      <c r="BH2" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="BI2" s="8" t="s">
+      <c r="BI2" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="BJ2" s="8" t="s">
+      <c r="BJ2" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="BK2" s="8" t="s">
+      <c r="BK2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="BL2" s="8" t="s">
+      <c r="BL2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="BM2" s="8" t="s">
+      <c r="BM2" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="BN2" s="8" t="s">
+      <c r="BN2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="BO2" s="8" t="s">
+      <c r="BO2" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="BP2" s="8" t="s">
+      <c r="BP2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="BQ2" s="8" t="s">
+      <c r="BQ2" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="BR2" s="8" t="s">
+      <c r="BR2" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:70" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="T3" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="V3" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="W3" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="X3" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Y3" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="Z3" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="AA3" s="9" t="s">
+      <c r="AA3" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AB3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="AC3" s="9" t="s">
+      <c r="AC3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AD3" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AE3" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AF3" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AG3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AH3" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AI3" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="AJ3" s="9" t="s">
+      <c r="AJ3" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="AK3" s="9" t="s">
+      <c r="AK3" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="AL3" s="9" t="s">
+      <c r="AL3" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="9" t="s">
+      <c r="AM3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AN3" s="9" t="s">
+      <c r="AN3" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="AO3" s="9" t="s">
+      <c r="AO3" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="AP3" s="9" t="s">
+      <c r="AP3" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="AQ3" s="9" t="s">
+      <c r="AQ3" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="AR3" s="9" t="s">
+      <c r="AR3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="AS3" s="9" t="s">
+      <c r="AS3" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="AT3" s="9" t="s">
+      <c r="AT3" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AU3" s="9" t="s">
+      <c r="AU3" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="AV3" s="9" t="s">
+      <c r="AV3" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="AW3" s="9" t="s">
+      <c r="AW3" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="AX3" s="9" t="s">
+      <c r="AX3" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="AY3" s="9" t="s">
+      <c r="AY3" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="AZ3" s="9" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="BA3" s="9" t="s">
+      <c r="BA3" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="BB3" s="9" t="s">
+      <c r="BB3" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="BC3" s="9" t="s">
+      <c r="BC3" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="BD3" s="9" t="s">
+      <c r="BD3" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="BE3" s="9" t="s">
+      <c r="BE3" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="BF3" s="9" t="s">
+      <c r="BF3" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="BG3" s="9" t="s">
+      <c r="BG3" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="BH3" s="9" t="s">
+      <c r="BH3" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="BI3" s="9" t="s">
+      <c r="BI3" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="BJ3" s="9" t="s">
+      <c r="BJ3" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="BK3" s="9" t="s">
+      <c r="BK3" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="BL3" s="9" t="s">
+      <c r="BL3" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="BM3" s="9" t="s">
+      <c r="BM3" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="BN3" s="9" t="s">
+      <c r="BN3" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="BO3" s="9" t="s">
+      <c r="BO3" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="BP3" s="9" t="s">
+      <c r="BP3" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="BQ3" s="9" t="s">
+      <c r="BQ3" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="BR3" s="9" t="s">
+      <c r="BR3" s="8" t="s">
         <v>210</v>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       <c r="BQ4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="BR4" s="7" t="s">
+      <c r="BR4" s="10" t="s">
         <v>60</v>
       </c>
     </row>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAD3628-68CC-4843-92C0-AD06134E6697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CEE1D5-1454-4CC6-B904-1A9EDF13D7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BR$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BS$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="216">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -699,6 +699,18 @@
   </si>
   <si>
     <t>{productionVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.conventionReserveQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{conventionReserveQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.conventionReserveQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1125,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BR4"/>
+  <dimension ref="A1:BS4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1143,16 +1155,16 @@
     <col min="18" max="19" width="5.4140625" customWidth="1"/>
     <col min="20" max="20" width="5.9140625" customWidth="1"/>
     <col min="21" max="23" width="5.75" customWidth="1"/>
-    <col min="24" max="32" width="6.33203125" customWidth="1"/>
-    <col min="33" max="33" width="8" customWidth="1"/>
-    <col min="34" max="34" width="7.08203125" customWidth="1"/>
-    <col min="35" max="69" width="6.08203125" customWidth="1"/>
-    <col min="70" max="70" width="8.4140625" customWidth="1"/>
-    <col min="71" max="74" width="6.08203125" customWidth="1"/>
-    <col min="75" max="76" width="16.75" customWidth="1"/>
+    <col min="24" max="33" width="6.33203125" customWidth="1"/>
+    <col min="34" max="34" width="8" customWidth="1"/>
+    <col min="35" max="35" width="7.08203125" customWidth="1"/>
+    <col min="36" max="70" width="6.08203125" customWidth="1"/>
+    <col min="71" max="71" width="8.4140625" customWidth="1"/>
+    <col min="72" max="75" width="6.08203125" customWidth="1"/>
+    <col min="76" max="77" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:71" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>140</v>
       </c>
@@ -1191,10 +1203,10 @@
       <c r="AH1" s="3"/>
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
-      <c r="AK1" s="3" t="s">
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
@@ -1218,21 +1230,22 @@
       <c r="BG1" s="3"/>
       <c r="BH1" s="3"/>
       <c r="BI1" s="3"/>
-      <c r="BJ1" s="3" t="s">
+      <c r="BJ1" s="3"/>
+      <c r="BK1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BK1" s="3"/>
       <c r="BL1" s="3"/>
       <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" s="3"/>
+      <c r="BP1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BP1" s="3"/>
       <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
+      <c r="BS1" s="3"/>
     </row>
-    <row r="2" spans="1:70" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:71" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>126</v>
       </c>
@@ -1315,136 +1328,139 @@
         <v>86</v>
       </c>
       <c r="AB2" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC2" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AE2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AF2" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AG2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AH2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="AH2" s="7" t="s">
+      <c r="AI2" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="AI2" s="7" t="s">
+      <c r="AJ2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="AJ2" s="7" t="s">
+      <c r="AK2" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AL2" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AM2" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="AM2" s="7" t="s">
+      <c r="AN2" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="AN2" s="7" t="s">
+      <c r="AO2" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AP2" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="AP2" s="7" t="s">
+      <c r="AQ2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="AQ2" s="7" t="s">
+      <c r="AR2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AR2" s="7" t="s">
+      <c r="AS2" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="AS2" s="7" t="s">
+      <c r="AT2" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="AT2" s="7" t="s">
+      <c r="AU2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="AU2" s="7" t="s">
+      <c r="AV2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AV2" s="7" t="s">
+      <c r="AW2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AW2" s="7" t="s">
+      <c r="AX2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AX2" s="7" t="s">
+      <c r="AY2" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AY2" s="7" t="s">
+      <c r="AZ2" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="AZ2" s="7" t="s">
+      <c r="BA2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="BA2" s="7" t="s">
+      <c r="BB2" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="BB2" s="7" t="s">
+      <c r="BC2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="BC2" s="7" t="s">
+      <c r="BD2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="BD2" s="7" t="s">
+      <c r="BE2" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="BE2" s="7" t="s">
+      <c r="BF2" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="BF2" s="7" t="s">
+      <c r="BG2" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="BG2" s="7" t="s">
+      <c r="BH2" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="BH2" s="7" t="s">
+      <c r="BI2" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="BI2" s="7" t="s">
+      <c r="BJ2" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="BJ2" s="7" t="s">
+      <c r="BK2" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="BK2" s="7" t="s">
+      <c r="BL2" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="BL2" s="7" t="s">
+      <c r="BM2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="BM2" s="7" t="s">
+      <c r="BN2" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="BN2" s="7" t="s">
+      <c r="BO2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="BO2" s="7" t="s">
+      <c r="BP2" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="BP2" s="7" t="s">
+      <c r="BQ2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="BQ2" s="7" t="s">
+      <c r="BR2" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="BR2" s="7" t="s">
+      <c r="BS2" s="7" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:70" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:71" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>141</v>
       </c>
@@ -1527,136 +1543,139 @@
         <v>167</v>
       </c>
       <c r="AB3" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="AC3" s="8" t="s">
+      <c r="AD3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="AD3" s="8" t="s">
+      <c r="AE3" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="AE3" s="8" t="s">
+      <c r="AF3" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="AF3" s="8" t="s">
+      <c r="AG3" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="AG3" s="8" t="s">
+      <c r="AH3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="AH3" s="8" t="s">
+      <c r="AI3" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="AI3" s="8" t="s">
+      <c r="AJ3" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="AJ3" s="8" t="s">
+      <c r="AK3" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="AK3" s="8" t="s">
+      <c r="AL3" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="AL3" s="8" t="s">
+      <c r="AM3" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="AM3" s="8" t="s">
+      <c r="AN3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="AN3" s="8" t="s">
+      <c r="AO3" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="AO3" s="8" t="s">
+      <c r="AP3" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="AP3" s="8" t="s">
+      <c r="AQ3" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="AQ3" s="8" t="s">
+      <c r="AR3" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="AR3" s="8" t="s">
+      <c r="AS3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="AS3" s="8" t="s">
+      <c r="AT3" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="AT3" s="8" t="s">
+      <c r="AU3" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AU3" s="8" t="s">
+      <c r="AV3" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="AW3" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="AX3" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="BA3" s="8" t="s">
+      <c r="BB3" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="BB3" s="8" t="s">
+      <c r="BC3" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="BC3" s="8" t="s">
+      <c r="BD3" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="BD3" s="8" t="s">
+      <c r="BE3" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="BE3" s="8" t="s">
+      <c r="BF3" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="BF3" s="8" t="s">
+      <c r="BG3" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="BG3" s="8" t="s">
+      <c r="BH3" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="BH3" s="8" t="s">
+      <c r="BI3" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="BI3" s="8" t="s">
+      <c r="BJ3" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="BJ3" s="8" t="s">
+      <c r="BK3" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="BK3" s="8" t="s">
+      <c r="BL3" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="BL3" s="8" t="s">
+      <c r="BM3" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="BM3" s="8" t="s">
+      <c r="BN3" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="BN3" s="8" t="s">
+      <c r="BO3" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="BO3" s="8" t="s">
+      <c r="BP3" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="BP3" s="8" t="s">
+      <c r="BQ3" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="BQ3" s="8" t="s">
+      <c r="BR3" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="BR3" s="8" t="s">
+      <c r="BS3" s="8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:70" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:71" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>130</v>
       </c>
@@ -1739,137 +1758,140 @@
         <v>47</v>
       </c>
       <c r="AB4" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AH4" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AI4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="AI4" s="5" t="s">
+      <c r="AJ4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AJ4" s="5" t="s">
+      <c r="AK4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="5" t="s">
+      <c r="AL4" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="AL4" s="5" t="s">
+      <c r="AM4" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="AM4" s="5" t="s">
+      <c r="AN4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="AN4" s="5" t="s">
+      <c r="AO4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AO4" s="5" t="s">
+      <c r="AP4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AP4" s="5" t="s">
+      <c r="AQ4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AQ4" s="5" t="s">
+      <c r="AR4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="AR4" s="5" t="s">
+      <c r="AS4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AS4" s="5" t="s">
+      <c r="AT4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AT4" s="5" t="s">
+      <c r="AU4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="AU4" s="5" t="s">
+      <c r="AV4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="AV4" s="5" t="s">
+      <c r="AW4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AW4" s="5" t="s">
+      <c r="AX4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AX4" s="5" t="s">
+      <c r="AY4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AY4" s="5" t="s">
+      <c r="AZ4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AZ4" s="5" t="s">
+      <c r="BA4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="BA4" s="5" t="s">
+      <c r="BB4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="BB4" s="5" t="s">
+      <c r="BC4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="BC4" s="5" t="s">
+      <c r="BD4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="BD4" s="5" t="s">
+      <c r="BE4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="BE4" s="5" t="s">
+      <c r="BF4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="BF4" s="5" t="s">
+      <c r="BG4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="BG4" s="5" t="s">
+      <c r="BH4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="BH4" s="5" t="s">
+      <c r="BI4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="BI4" s="5" t="s">
+      <c r="BJ4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="BJ4" s="5" t="s">
+      <c r="BK4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="BK4" s="5" t="s">
+      <c r="BL4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="BL4" s="5" t="s">
+      <c r="BM4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="BM4" s="5" t="s">
+      <c r="BN4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="BN4" s="5" t="s">
+      <c r="BO4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="BO4" s="5" t="s">
+      <c r="BP4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="BP4" s="5" t="s">
+      <c r="BQ4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="BQ4" s="5" t="s">
+      <c r="BR4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="BR4" s="10" t="s">
+      <c r="BS4" s="10" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BR4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BS4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CEE1D5-1454-4CC6-B904-1A9EDF13D7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22185CE4-1F82-4AE6-B350-35F74C3C60C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -718,6 +718,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -830,7 +834,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,9 +853,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -859,8 +860,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1165,7 +1177,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>140</v>
       </c>
       <c r="B1" s="4"/>
@@ -1246,437 +1258,437 @@
       <c r="BS1" s="3"/>
     </row>
     <row r="2" spans="1:71" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="V2" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="W2" s="7" t="s">
+      <c r="W2" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="X2" s="7" t="s">
+      <c r="X2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="7" t="s">
+      <c r="Y2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="Z2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AA2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AB2" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AC2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AD2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AE2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="AF2" s="7" t="s">
+      <c r="AF2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AG2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AH2" s="7" t="s">
+      <c r="AH2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="7" t="s">
+      <c r="AI2" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="AJ2" s="7" t="s">
+      <c r="AJ2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" s="7" t="s">
+      <c r="AK2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AL2" s="7" t="s">
+      <c r="AL2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AM2" s="7" t="s">
+      <c r="AM2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AN2" s="7" t="s">
+      <c r="AN2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AO2" s="7" t="s">
+      <c r="AO2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AP2" s="7" t="s">
+      <c r="AP2" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AQ2" s="7" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AR2" s="7" t="s">
+      <c r="AR2" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AS2" s="7" t="s">
+      <c r="AS2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AT2" s="7" t="s">
+      <c r="AT2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AU2" s="7" t="s">
+      <c r="AU2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AV2" s="7" t="s">
+      <c r="AV2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AW2" s="7" t="s">
+      <c r="AW2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AX2" s="7" t="s">
+      <c r="AX2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="AY2" s="7" t="s">
+      <c r="AY2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AZ2" s="7" t="s">
+      <c r="AZ2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="BA2" s="7" t="s">
+      <c r="BA2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="BB2" s="7" t="s">
+      <c r="BB2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" s="7" t="s">
+      <c r="BC2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="BD2" s="7" t="s">
+      <c r="BD2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="BE2" s="7" t="s">
+      <c r="BE2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="BF2" s="7" t="s">
+      <c r="BF2" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="BG2" s="7" t="s">
+      <c r="BG2" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BH2" s="7" t="s">
+      <c r="BH2" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="BI2" s="7" t="s">
+      <c r="BI2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BJ2" s="7" t="s">
+      <c r="BJ2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BK2" s="7" t="s">
+      <c r="BK2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BL2" s="7" t="s">
+      <c r="BL2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="BM2" s="7" t="s">
+      <c r="BM2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="BN2" s="7" t="s">
+      <c r="BN2" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="BO2" s="7" t="s">
+      <c r="BO2" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="BP2" s="7" t="s">
+      <c r="BP2" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="BQ2" s="7" t="s">
+      <c r="BQ2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="BR2" s="7" t="s">
+      <c r="BR2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="BS2" s="7" t="s">
+      <c r="BS2" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:71" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="U3" s="8" t="s">
+      <c r="U3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="V3" s="8" t="s">
+      <c r="V3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="W3" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="X3" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="Y3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Z3" s="8" t="s">
+      <c r="Z3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="AA3" s="8" t="s">
+      <c r="AA3" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="AB3" s="8" t="s">
+      <c r="AB3" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="AC3" s="8" t="s">
+      <c r="AC3" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="AD3" s="8" t="s">
+      <c r="AD3" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="AE3" s="8" t="s">
+      <c r="AE3" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="AF3" s="8" t="s">
+      <c r="AF3" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AG3" s="8" t="s">
+      <c r="AG3" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AH3" s="8" t="s">
+      <c r="AH3" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AI3" s="8" t="s">
+      <c r="AI3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AJ3" s="8" t="s">
+      <c r="AJ3" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AK3" s="8" t="s">
+      <c r="AK3" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AL3" s="8" t="s">
+      <c r="AL3" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AM3" s="8" t="s">
+      <c r="AM3" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AN3" s="8" t="s">
+      <c r="AN3" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="AO3" s="8" t="s">
+      <c r="AO3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="AP3" s="8" t="s">
+      <c r="AP3" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="AQ3" s="8" t="s">
+      <c r="AQ3" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="AR3" s="8" t="s">
+      <c r="AR3" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="AS3" s="8" t="s">
+      <c r="AS3" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="AT3" s="8" t="s">
+      <c r="AT3" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="AU3" s="8" t="s">
+      <c r="AU3" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="AV3" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="AW3" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="AX3" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="AY3" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="BA3" s="8" t="s">
+      <c r="BA3" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="BB3" s="8" t="s">
+      <c r="BB3" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="BC3" s="8" t="s">
+      <c r="BC3" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="BD3" s="8" t="s">
+      <c r="BD3" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="BE3" s="8" t="s">
+      <c r="BE3" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="BF3" s="8" t="s">
+      <c r="BF3" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="BG3" s="8" t="s">
+      <c r="BG3" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="BH3" s="8" t="s">
+      <c r="BH3" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="BI3" s="8" t="s">
+      <c r="BI3" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="BJ3" s="8" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="BK3" s="8" t="s">
+      <c r="BK3" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="BL3" s="8" t="s">
+      <c r="BL3" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="BM3" s="8" t="s">
+      <c r="BM3" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="BN3" s="8" t="s">
+      <c r="BN3" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="BO3" s="8" t="s">
+      <c r="BO3" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="BP3" s="8" t="s">
+      <c r="BP3" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="BQ3" s="8" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="BR3" s="8" t="s">
+      <c r="BR3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="BS3" s="8" t="s">
+      <c r="BS3" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:71" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>130</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1727,166 +1739,166 @@
       <c r="Q4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="V4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="Z4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AA4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AB4" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AC4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AD4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AE4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AF4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AG4" s="5" t="s">
+      <c r="AG4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AH4" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AI4" s="5" t="s">
+      <c r="AI4" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="AJ4" s="5" t="s">
+      <c r="AJ4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AK4" s="5" t="s">
+      <c r="AK4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AL4" s="5" t="s">
+      <c r="AL4" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="AM4" s="5" t="s">
+      <c r="AM4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="AN4" s="5" t="s">
+      <c r="AN4" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="AO4" s="5" t="s">
+      <c r="AO4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="5" t="s">
+      <c r="AP4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AQ4" s="5" t="s">
+      <c r="AQ4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="AR4" s="5" t="s">
+      <c r="AR4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AS4" s="5" t="s">
+      <c r="AS4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="AT4" s="5" t="s">
+      <c r="AT4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AU4" s="5" t="s">
+      <c r="AU4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AV4" s="5" t="s">
+      <c r="AV4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AW4" s="5" t="s">
+      <c r="AW4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AX4" s="5" t="s">
+      <c r="AX4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AY4" s="5" t="s">
+      <c r="AY4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AZ4" s="5" t="s">
+      <c r="AZ4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BA4" s="5" t="s">
+      <c r="BA4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BB4" s="5" t="s">
+      <c r="BB4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BC4" s="5" t="s">
+      <c r="BC4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="BD4" s="5" t="s">
+      <c r="BD4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="BE4" s="5" t="s">
+      <c r="BE4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="BF4" s="5" t="s">
+      <c r="BF4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="BG4" s="5" t="s">
+      <c r="BG4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="BH4" s="5" t="s">
+      <c r="BH4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="BI4" s="5" t="s">
+      <c r="BI4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BJ4" s="5" t="s">
+      <c r="BJ4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BK4" s="5" t="s">
+      <c r="BK4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="BL4" s="5" t="s">
+      <c r="BL4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="BM4" s="5" t="s">
+      <c r="BM4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="BN4" s="5" t="s">
+      <c r="BN4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="BO4" s="5" t="s">
+      <c r="BO4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="BP4" s="5" t="s">
+      <c r="BP4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="BQ4" s="5" t="s">
+      <c r="BQ4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="BR4" s="5" t="s">
+      <c r="BR4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="BS4" s="10" t="s">
+      <c r="BS4" s="11" t="s">
         <v>60</v>
       </c>
     </row>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22185CE4-1F82-4AE6-B350-35F74C3C60C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C5DE91-02C5-44E6-A384-870F3F41CA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="218">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -711,6 +711,14 @@
   </si>
   <si>
     <t>{.conventionReserveQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{specialMaterialResult}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.specialMaterialResult}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1149,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BS4"/>
+  <dimension ref="A1:BS7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1902,6 +1910,16 @@
         <v>60</v>
       </c>
     </row>
+    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:BS4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C5DE91-02C5-44E6-A384-870F3F41CA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F16118-1379-4292-8228-8AE3AA3096A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1174,8 +1174,8 @@
     <col min="17" max="17" width="7.83203125" customWidth="1"/>
     <col min="18" max="19" width="5.4140625" customWidth="1"/>
     <col min="20" max="20" width="5.9140625" customWidth="1"/>
-    <col min="21" max="23" width="5.75" customWidth="1"/>
-    <col min="24" max="33" width="6.33203125" customWidth="1"/>
+    <col min="21" max="22" width="5.75" customWidth="1"/>
+    <col min="23" max="33" width="6.33203125" customWidth="1"/>
     <col min="34" max="34" width="8" customWidth="1"/>
     <col min="35" max="35" width="7.08203125" customWidth="1"/>
     <col min="36" max="70" width="6.08203125" customWidth="1"/>
@@ -1345,10 +1345,10 @@
         <v>85</v>
       </c>
       <c r="AA2" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="AB2" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="AB2" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="AC2" s="12" t="s">
         <v>87</v>
@@ -1560,10 +1560,10 @@
         <v>166</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>214</v>
       </c>
       <c r="AC3" s="7" t="s">
         <v>168</v>
@@ -1775,10 +1775,10 @@
         <v>59</v>
       </c>
       <c r="AA4" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB4" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>215</v>
       </c>
       <c r="AC4" s="9" t="s">
         <v>46</v>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F16118-1379-4292-8228-8AE3AA3096A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB15260-72BC-437C-8BEB-6878EE73B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -719,6 +719,10 @@
   </si>
   <si>
     <t>{.specialMaterialResult}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.differenceQtyA}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1369,7 +1373,7 @@
         <v>137</v>
       </c>
       <c r="AI2" s="12" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="AJ2" s="12" t="s">
         <v>92</v>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB15260-72BC-437C-8BEB-6878EE73B30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AF5221-E01C-42BA-9F77-919244183537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BS$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BU$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -723,6 +723,30 @@
   </si>
   <si>
     <t>{.differenceQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unRestrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{unRestrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unRestrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQty}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1161,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BS7"/>
+  <dimension ref="A1:BU7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1179,16 +1203,16 @@
     <col min="18" max="19" width="5.4140625" customWidth="1"/>
     <col min="20" max="20" width="5.9140625" customWidth="1"/>
     <col min="21" max="22" width="5.75" customWidth="1"/>
-    <col min="23" max="33" width="6.33203125" customWidth="1"/>
-    <col min="34" max="34" width="8" customWidth="1"/>
-    <col min="35" max="35" width="7.08203125" customWidth="1"/>
-    <col min="36" max="70" width="6.08203125" customWidth="1"/>
-    <col min="71" max="71" width="8.4140625" customWidth="1"/>
-    <col min="72" max="75" width="6.08203125" customWidth="1"/>
-    <col min="76" max="77" width="16.75" customWidth="1"/>
+    <col min="23" max="35" width="6.33203125" customWidth="1"/>
+    <col min="36" max="36" width="8" customWidth="1"/>
+    <col min="37" max="37" width="7.08203125" customWidth="1"/>
+    <col min="38" max="72" width="6.08203125" customWidth="1"/>
+    <col min="73" max="73" width="8.4140625" customWidth="1"/>
+    <col min="74" max="77" width="6.08203125" customWidth="1"/>
+    <col min="78" max="79" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:73" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>140</v>
       </c>
@@ -1228,11 +1252,11 @@
       <c r="AI1" s="3"/>
       <c r="AJ1" s="3"/>
       <c r="AK1" s="3"/>
-      <c r="AL1" s="3" t="s">
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3"/>
@@ -1255,21 +1279,23 @@
       <c r="BH1" s="3"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="3"/>
-      <c r="BK1" s="3" t="s">
+      <c r="BK1" s="3"/>
+      <c r="BL1" s="3"/>
+      <c r="BM1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="BL1" s="3"/>
-      <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
       <c r="BO1" s="3"/>
-      <c r="BP1" s="3" t="s">
+      <c r="BP1" s="3"/>
+      <c r="BQ1" s="3"/>
+      <c r="BR1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="BQ1" s="3"/>
-      <c r="BR1" s="3"/>
       <c r="BS1" s="3"/>
+      <c r="BT1" s="3"/>
+      <c r="BU1" s="3"/>
     </row>
-    <row r="2" spans="1:71" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:73" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>126</v>
       </c>
@@ -1340,151 +1366,157 @@
         <v>82</v>
       </c>
       <c r="X2" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="Y2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="AA2" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="AA2" s="12" t="s">
+      <c r="AB2" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="AB2" s="12" t="s">
+      <c r="AC2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AD2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AE2" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AF2" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AG2" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="AG2" s="12" t="s">
+      <c r="AH2" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="AH2" s="12" t="s">
+      <c r="AI2" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="AI2" s="12" t="s">
+      <c r="AK2" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="AJ2" s="12" t="s">
+      <c r="AL2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AM2" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AL2" s="12" t="s">
+      <c r="AN2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AM2" s="12" t="s">
+      <c r="AO2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="AN2" s="12" t="s">
+      <c r="AP2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AO2" s="12" t="s">
+      <c r="AQ2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AP2" s="12" t="s">
+      <c r="AR2" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="AS2" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AR2" s="12" t="s">
+      <c r="AT2" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AS2" s="12" t="s">
+      <c r="AU2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="AV2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="AW2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="AX2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AW2" s="12" t="s">
+      <c r="AY2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AX2" s="12" t="s">
+      <c r="AZ2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="AY2" s="12" t="s">
+      <c r="BA2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="BB2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BC2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="BB2" s="12" t="s">
+      <c r="BD2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="BC2" s="12" t="s">
+      <c r="BE2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="BD2" s="12" t="s">
+      <c r="BF2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="BE2" s="12" t="s">
+      <c r="BG2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="BF2" s="12" t="s">
+      <c r="BH2" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="BG2" s="12" t="s">
+      <c r="BI2" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BH2" s="12" t="s">
+      <c r="BJ2" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="BK2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BJ2" s="12" t="s">
+      <c r="BL2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BK2" s="12" t="s">
+      <c r="BM2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BL2" s="12" t="s">
+      <c r="BN2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="BM2" s="12" t="s">
+      <c r="BO2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="BN2" s="12" t="s">
+      <c r="BP2" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="BO2" s="12" t="s">
+      <c r="BQ2" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="BP2" s="12" t="s">
+      <c r="BR2" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="BQ2" s="12" t="s">
+      <c r="BS2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="BR2" s="12" t="s">
+      <c r="BT2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="BU2" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:71" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:73" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>141</v>
       </c>
@@ -1555,151 +1587,157 @@
         <v>163</v>
       </c>
       <c r="X3" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y3" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AE3" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AF3" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AG3" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AH3" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AI3" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AK3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AL3" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AK3" s="7" t="s">
+      <c r="AM3" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AN3" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AO3" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AP3" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AQ3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AR3" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="AS3" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="AT3" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="AU3" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="AV3" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="AW3" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="AX3" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="AY3" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="BA3" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="BB3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BC3" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BD3" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BE3" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BF3" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BG3" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BH3" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BI3" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BK3" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BL3" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BM3" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BN3" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BO3" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BP3" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BR3" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="BS3" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="BS3" s="7" t="s">
+      <c r="BU3" s="7" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:71" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:73" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>130</v>
       </c>
@@ -1770,162 +1808,168 @@
         <v>48</v>
       </c>
       <c r="X4" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Z4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AB4" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AC4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="AC4" s="9" t="s">
+      <c r="AD4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AD4" s="9" t="s">
+      <c r="AE4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AE4" s="9" t="s">
+      <c r="AF4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AF4" s="9" t="s">
+      <c r="AG4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="AG4" s="9" t="s">
+      <c r="AH4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AH4" s="9" t="s">
+      <c r="AI4" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AI4" s="9" t="s">
+      <c r="AK4" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="AJ4" s="9" t="s">
+      <c r="AL4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="AK4" s="9" t="s">
+      <c r="AM4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AL4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="AM4" s="9" t="s">
+      <c r="AO4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="AN4" s="9" t="s">
+      <c r="AP4" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="AO4" s="9" t="s">
+      <c r="AQ4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="9" t="s">
+      <c r="AR4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AQ4" s="9" t="s">
+      <c r="AS4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="AR4" s="9" t="s">
+      <c r="AT4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AS4" s="9" t="s">
+      <c r="AU4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="AT4" s="9" t="s">
+      <c r="AV4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AU4" s="9" t="s">
+      <c r="AW4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AV4" s="9" t="s">
+      <c r="AX4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AW4" s="9" t="s">
+      <c r="AY4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AX4" s="9" t="s">
+      <c r="AZ4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AY4" s="9" t="s">
+      <c r="BA4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AZ4" s="9" t="s">
+      <c r="BB4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BA4" s="9" t="s">
+      <c r="BC4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BB4" s="9" t="s">
+      <c r="BD4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BC4" s="9" t="s">
+      <c r="BE4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="BD4" s="9" t="s">
+      <c r="BF4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="BE4" s="9" t="s">
+      <c r="BG4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="BF4" s="9" t="s">
+      <c r="BH4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="BG4" s="9" t="s">
+      <c r="BI4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="BH4" s="9" t="s">
+      <c r="BJ4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="BI4" s="9" t="s">
+      <c r="BK4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BJ4" s="9" t="s">
+      <c r="BL4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BK4" s="9" t="s">
+      <c r="BM4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="BL4" s="9" t="s">
+      <c r="BN4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="BM4" s="9" t="s">
+      <c r="BO4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="BN4" s="9" t="s">
+      <c r="BP4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="BO4" s="9" t="s">
+      <c r="BQ4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="BP4" s="9" t="s">
+      <c r="BR4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="BQ4" s="9" t="s">
+      <c r="BS4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="BR4" s="9" t="s">
+      <c r="BT4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="BS4" s="11" t="s">
+      <c r="BU4" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>217</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BS4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BU4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/factoryMonthPlanMouldDayResultExportTemp.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\jy_aps\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AF5221-E01C-42BA-9F77-919244183537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3B75E4-FD05-45AC-8CDF-17543E44509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$BU$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">月计划!$A$4:$CC$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t>{.materialCode}</t>
   </si>
@@ -455,298 +455,374 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{.lastDay1A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.actualOrderUnproducedA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.actualOrderUnproduced}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.differenceQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{factoryName}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{locationType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{materialCode}</t>
+  </si>
+  <si>
+    <t>{mesMaterialCode}</t>
+  </si>
+  <si>
+    <t>{materialDesc}</t>
+  </si>
+  <si>
+    <t>{structureName}</t>
+  </si>
+  <si>
+    <t>{structureType}</t>
+  </si>
+  <si>
+    <t>{productStatus}</t>
+  </si>
+  <si>
+    <t>{embryoCode}</t>
+  </si>
+  <si>
+    <t>{mainMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{constructionStage}</t>
+  </si>
+  <si>
+    <t>{brand}</t>
+  </si>
+  <si>
+    <t>{specifications}</t>
+  </si>
+  <si>
+    <t>{mainPattern}</t>
+  </si>
+  <si>
+    <t>{pattern}</t>
+  </si>
+  <si>
+    <t>{proSize}</t>
+  </si>
+  <si>
+    <t>{singleTireWeight}</t>
+  </si>
+  <si>
+    <t>{productCategory}</t>
+  </si>
+  <si>
+    <t>{mouldCavityQty}</t>
+  </si>
+  <si>
+    <t>{typeBlockQty}</t>
+  </si>
+  <si>
+    <t>{averageSaleQty}</t>
+  </si>
+  <si>
+    <t>{inventorySalesRatio}</t>
+  </si>
+  <si>
+    <t>{dayVulcanizationQty}</t>
+  </si>
+  <si>
+    <t>{prodReqPlan}</t>
+  </si>
+  <si>
+    <t>{heightQty}</t>
+  </si>
+  <si>
+    <t>{midQty}</t>
+  </si>
+  <si>
+    <t>{cycleReserveQty}</t>
+  </si>
+  <si>
+    <t>{totalQty}</t>
+  </si>
+  <si>
+    <t>{heightProductionQty}</t>
+  </si>
+  <si>
+    <t>{midProductionQty}</t>
+  </si>
+  <si>
+    <t>{cycleProductionQty}</t>
+  </si>
+  <si>
+    <t>{conventionProductionQty}</t>
+  </si>
+  <si>
+    <t>{postponeProductionQty}</t>
+  </si>
+  <si>
+    <t>{actualOrderUnproduced}</t>
+  </si>
+  <si>
+    <t>{differenceQty}</t>
+  </si>
+  <si>
+    <t>{beginDay}</t>
+  </si>
+  <si>
+    <t>{endDay}</t>
+  </si>
+  <si>
+    <t>{lastDay2}</t>
+  </si>
+  <si>
+    <t>{lastDay1}</t>
+  </si>
+  <si>
+    <t>{day1}</t>
+  </si>
+  <si>
+    <t>{day2}</t>
+  </si>
+  <si>
+    <t>{day3}</t>
+  </si>
+  <si>
+    <t>{day4}</t>
+  </si>
+  <si>
+    <t>{day5}</t>
+  </si>
+  <si>
+    <t>{day6}</t>
+  </si>
+  <si>
+    <t>{day7}</t>
+  </si>
+  <si>
+    <t>{day8}</t>
+  </si>
+  <si>
+    <t>{day9}</t>
+  </si>
+  <si>
+    <t>{day10}</t>
+  </si>
+  <si>
+    <t>{day11}</t>
+  </si>
+  <si>
+    <t>{day12}</t>
+  </si>
+  <si>
+    <t>{day13}</t>
+  </si>
+  <si>
+    <t>{day14}</t>
+  </si>
+  <si>
+    <t>{day15}</t>
+  </si>
+  <si>
+    <t>{day16}</t>
+  </si>
+  <si>
+    <t>{day17}</t>
+  </si>
+  <si>
+    <t>{day18}</t>
+  </si>
+  <si>
+    <t>{day19}</t>
+  </si>
+  <si>
+    <t>{day20}</t>
+  </si>
+  <si>
+    <t>{day21}</t>
+  </si>
+  <si>
+    <t>{day22}</t>
+  </si>
+  <si>
+    <t>{day23}</t>
+  </si>
+  <si>
+    <t>{day24}</t>
+  </si>
+  <si>
+    <t>{day25}</t>
+  </si>
+  <si>
+    <t>{day26}</t>
+  </si>
+  <si>
+    <t>{day27}</t>
+  </si>
+  <si>
+    <t>{day28}</t>
+  </si>
+  <si>
+    <t>{day29}</t>
+  </si>
+  <si>
+    <t>{day30}</t>
+  </si>
+  <si>
+    <t>{day31}</t>
+  </si>
+  <si>
+    <t>{totalAll}</t>
+  </si>
+  <si>
+    <t>{monthPlanVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{productionVersion}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.conventionReserveQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{conventionReserveQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.conventionReserveQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{specialMaterialResult}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.specialMaterialResult}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.differenceQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unRestrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{unRestrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unRestrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQtyA}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.restrictedNetQty}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay8}</t>
+  </si>
+  <si>
+    <t>{lastDay7}</t>
+  </si>
+  <si>
+    <t>{lastDay6}</t>
+  </si>
+  <si>
+    <t>{lastDay5}</t>
+  </si>
+  <si>
+    <t>{lastDay4}</t>
+  </si>
+  <si>
+    <t>{lastDay3}</t>
+  </si>
+  <si>
+    <t>{.lastDay8A}</t>
+  </si>
+  <si>
+    <t>{.lastDay7A}</t>
+  </si>
+  <si>
+    <t>{.lastDay6A}</t>
+  </si>
+  <si>
+    <t>{.lastDay5A}</t>
+  </si>
+  <si>
+    <t>{.lastDay4A}</t>
+  </si>
+  <si>
+    <t>{.lastDay3A}</t>
+  </si>
+  <si>
+    <t>{.lastDay2A}</t>
+  </si>
+  <si>
+    <t>{.lastDay8}</t>
+  </si>
+  <si>
+    <t>{.lastDay7}</t>
+  </si>
+  <si>
+    <t>{.lastDay6}</t>
+  </si>
+  <si>
+    <t>{.lastDay5}</t>
+  </si>
+  <si>
+    <t>{.lastDay4}</t>
+  </si>
+  <si>
+    <t>{.lastDay3}</t>
+  </si>
+  <si>
     <t>{.lastDay2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay2A}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.lastDay1A}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproducedA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.actualOrderUnproduced}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.differenceQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{factoryName}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{locationType}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{materialCode}</t>
-  </si>
-  <si>
-    <t>{mesMaterialCode}</t>
-  </si>
-  <si>
-    <t>{materialDesc}</t>
-  </si>
-  <si>
-    <t>{structureName}</t>
-  </si>
-  <si>
-    <t>{structureType}</t>
-  </si>
-  <si>
-    <t>{productStatus}</t>
-  </si>
-  <si>
-    <t>{embryoCode}</t>
-  </si>
-  <si>
-    <t>{mainMaterialDesc}</t>
-  </si>
-  <si>
-    <t>{constructionStage}</t>
-  </si>
-  <si>
-    <t>{brand}</t>
-  </si>
-  <si>
-    <t>{specifications}</t>
-  </si>
-  <si>
-    <t>{mainPattern}</t>
-  </si>
-  <si>
-    <t>{pattern}</t>
-  </si>
-  <si>
-    <t>{proSize}</t>
-  </si>
-  <si>
-    <t>{singleTireWeight}</t>
-  </si>
-  <si>
-    <t>{productCategory}</t>
-  </si>
-  <si>
-    <t>{mouldCavityQty}</t>
-  </si>
-  <si>
-    <t>{typeBlockQty}</t>
-  </si>
-  <si>
-    <t>{averageSaleQty}</t>
-  </si>
-  <si>
-    <t>{inventorySalesRatio}</t>
-  </si>
-  <si>
-    <t>{dayVulcanizationQty}</t>
-  </si>
-  <si>
-    <t>{prodReqPlan}</t>
-  </si>
-  <si>
-    <t>{heightQty}</t>
-  </si>
-  <si>
-    <t>{midQty}</t>
-  </si>
-  <si>
-    <t>{cycleReserveQty}</t>
-  </si>
-  <si>
-    <t>{totalQty}</t>
-  </si>
-  <si>
-    <t>{heightProductionQty}</t>
-  </si>
-  <si>
-    <t>{midProductionQty}</t>
-  </si>
-  <si>
-    <t>{cycleProductionQty}</t>
-  </si>
-  <si>
-    <t>{conventionProductionQty}</t>
-  </si>
-  <si>
-    <t>{postponeProductionQty}</t>
-  </si>
-  <si>
-    <t>{actualOrderUnproduced}</t>
-  </si>
-  <si>
-    <t>{differenceQty}</t>
-  </si>
-  <si>
-    <t>{beginDay}</t>
-  </si>
-  <si>
-    <t>{endDay}</t>
-  </si>
-  <si>
-    <t>{lastDay2}</t>
-  </si>
-  <si>
-    <t>{lastDay1}</t>
-  </si>
-  <si>
-    <t>{day1}</t>
-  </si>
-  <si>
-    <t>{day2}</t>
-  </si>
-  <si>
-    <t>{day3}</t>
-  </si>
-  <si>
-    <t>{day4}</t>
-  </si>
-  <si>
-    <t>{day5}</t>
-  </si>
-  <si>
-    <t>{day6}</t>
-  </si>
-  <si>
-    <t>{day7}</t>
-  </si>
-  <si>
-    <t>{day8}</t>
-  </si>
-  <si>
-    <t>{day9}</t>
-  </si>
-  <si>
-    <t>{day10}</t>
-  </si>
-  <si>
-    <t>{day11}</t>
-  </si>
-  <si>
-    <t>{day12}</t>
-  </si>
-  <si>
-    <t>{day13}</t>
-  </si>
-  <si>
-    <t>{day14}</t>
-  </si>
-  <si>
-    <t>{day15}</t>
-  </si>
-  <si>
-    <t>{day16}</t>
-  </si>
-  <si>
-    <t>{day17}</t>
-  </si>
-  <si>
-    <t>{day18}</t>
-  </si>
-  <si>
-    <t>{day19}</t>
-  </si>
-  <si>
-    <t>{day20}</t>
-  </si>
-  <si>
-    <t>{day21}</t>
-  </si>
-  <si>
-    <t>{day22}</t>
-  </si>
-  <si>
-    <t>{day23}</t>
-  </si>
-  <si>
-    <t>{day24}</t>
-  </si>
-  <si>
-    <t>{day25}</t>
-  </si>
-  <si>
-    <t>{day26}</t>
-  </si>
-  <si>
-    <t>{day27}</t>
-  </si>
-  <si>
-    <t>{day28}</t>
-  </si>
-  <si>
-    <t>{day29}</t>
-  </si>
-  <si>
-    <t>{day30}</t>
-  </si>
-  <si>
-    <t>{day31}</t>
-  </si>
-  <si>
-    <t>{totalAll}</t>
-  </si>
-  <si>
-    <t>{monthPlanVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{productionVersion}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.conventionReserveQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{conventionReserveQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.conventionReserveQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{specialMaterialResult}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.specialMaterialResult}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.differenceQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.unRestrictedNetQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{unRestrictedNetQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.unRestrictedNetQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.restrictedNetQtyA}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{restrictedNetQty}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.restrictedNetQty}</t>
+  </si>
+  <si>
+    <t>{.lastDay9A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay9}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay9}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay10A}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{lastDay10}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.lastDay10}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1185,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BU7"/>
+  <dimension ref="A1:CC7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1206,15 +1282,15 @@
     <col min="23" max="35" width="6.33203125" customWidth="1"/>
     <col min="36" max="36" width="8" customWidth="1"/>
     <col min="37" max="37" width="7.08203125" customWidth="1"/>
-    <col min="38" max="72" width="6.08203125" customWidth="1"/>
-    <col min="73" max="73" width="8.4140625" customWidth="1"/>
-    <col min="74" max="77" width="6.08203125" customWidth="1"/>
-    <col min="78" max="79" width="16.75" customWidth="1"/>
+    <col min="38" max="80" width="6.08203125" customWidth="1"/>
+    <col min="81" max="81" width="8.4140625" customWidth="1"/>
+    <col min="82" max="85" width="6.08203125" customWidth="1"/>
+    <col min="86" max="87" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:81" s="2" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="3"/>
@@ -1254,9 +1330,7 @@
       <c r="AK1" s="3"/>
       <c r="AL1" s="3"/>
       <c r="AM1" s="3"/>
-      <c r="AN1" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="AN1" s="3"/>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3"/>
@@ -1264,7 +1338,9 @@
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
       <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
+      <c r="AV1" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="AW1" s="3"/>
       <c r="AX1" s="3"/>
       <c r="AY1" s="3"/>
@@ -1281,21 +1357,29 @@
       <c r="BJ1" s="3"/>
       <c r="BK1" s="3"/>
       <c r="BL1" s="3"/>
-      <c r="BM1" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="BM1" s="3"/>
       <c r="BN1" s="3"/>
       <c r="BO1" s="3"/>
       <c r="BP1" s="3"/>
       <c r="BQ1" s="3"/>
-      <c r="BR1" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="BR1" s="3"/>
       <c r="BS1" s="3"/>
       <c r="BT1" s="3"/>
-      <c r="BU1" s="3"/>
+      <c r="BU1" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="BV1" s="3"/>
+      <c r="BW1" s="3"/>
+      <c r="BX1" s="3"/>
+      <c r="BY1" s="3"/>
+      <c r="BZ1" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="CA1" s="3"/>
+      <c r="CB1" s="3"/>
+      <c r="CC1" s="3"/>
     </row>
-    <row r="2" spans="1:73" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:81" s="2" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>126</v>
       </c>
@@ -1366,7 +1450,7 @@
         <v>82</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Y2" s="12" t="s">
         <v>83</v>
@@ -1378,7 +1462,7 @@
         <v>85</v>
       </c>
       <c r="AB2" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AC2" s="12" t="s">
         <v>86</v>
@@ -1399,13 +1483,13 @@
         <v>91</v>
       </c>
       <c r="AI2" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AJ2" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AK2" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AL2" s="12" t="s">
         <v>92</v>
@@ -1414,330 +1498,378 @@
         <v>93</v>
       </c>
       <c r="AN2" s="12" t="s">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="AO2" s="12" t="s">
-        <v>136</v>
+        <v>243</v>
       </c>
       <c r="AP2" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="AR2" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="AS2" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="AT2" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="AU2" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="AV2" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="AW2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="AX2" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AQ2" s="12" t="s">
+      <c r="AY2" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AR2" s="12" t="s">
+      <c r="AZ2" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AS2" s="12" t="s">
+      <c r="BA2" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AT2" s="12" t="s">
+      <c r="BB2" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="AU2" s="12" t="s">
+      <c r="BC2" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="AV2" s="12" t="s">
+      <c r="BD2" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="AW2" s="12" t="s">
+      <c r="BE2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="AX2" s="12" t="s">
+      <c r="BF2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AY2" s="12" t="s">
+      <c r="BG2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AZ2" s="12" t="s">
+      <c r="BH2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="BA2" s="12" t="s">
+      <c r="BI2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BB2" s="12" t="s">
+      <c r="BJ2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="BC2" s="12" t="s">
+      <c r="BK2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="BD2" s="12" t="s">
+      <c r="BL2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="BE2" s="12" t="s">
+      <c r="BM2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="BF2" s="12" t="s">
+      <c r="BN2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="BG2" s="12" t="s">
+      <c r="BO2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="BH2" s="12" t="s">
+      <c r="BP2" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="BI2" s="12" t="s">
+      <c r="BQ2" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BJ2" s="12" t="s">
+      <c r="BR2" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="BK2" s="12" t="s">
+      <c r="BS2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BL2" s="12" t="s">
+      <c r="BT2" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BM2" s="12" t="s">
+      <c r="BU2" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BN2" s="12" t="s">
+      <c r="BV2" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="BO2" s="12" t="s">
+      <c r="BW2" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="BP2" s="12" t="s">
+      <c r="BX2" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="BQ2" s="12" t="s">
+      <c r="BY2" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="BR2" s="12" t="s">
+      <c r="BZ2" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="BS2" s="12" t="s">
+      <c r="CA2" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="BT2" s="12" t="s">
+      <c r="CB2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="BU2" s="12" t="s">
+      <c r="CC2" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:73" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:81" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="X3" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y3" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="Z3" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="X3" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="Y3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="AB3" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="AC3" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="AB3" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AE3" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="AD3" s="7" t="s">
+      <c r="AF3" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="AE3" s="7" t="s">
+      <c r="AG3" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="AF3" s="7" t="s">
+      <c r="AH3" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="AG3" s="7" t="s">
+      <c r="AI3" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="AH3" s="7" t="s">
+      <c r="AK3" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="AI3" s="7" t="s">
+      <c r="AL3" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="AM3" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="AO3" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="AP3" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="AJ3" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="AK3" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="AL3" s="7" t="s">
+      <c r="AQ3" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="AS3" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="AT3" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AU3" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="AV3" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="AM3" s="7" t="s">
+      <c r="AW3" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="AN3" s="7" t="s">
+      <c r="AX3" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AO3" s="7" t="s">
+      <c r="AY3" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="AP3" s="7" t="s">
+      <c r="AZ3" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="AQ3" s="7" t="s">
+      <c r="BA3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="AR3" s="7" t="s">
+      <c r="BB3" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="AS3" s="7" t="s">
+      <c r="BC3" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="AT3" s="7" t="s">
+      <c r="BD3" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="AU3" s="7" t="s">
+      <c r="BE3" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="AV3" s="7" t="s">
+      <c r="BF3" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="AW3" s="7" t="s">
+      <c r="BG3" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="AX3" s="7" t="s">
+      <c r="BH3" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="AY3" s="7" t="s">
+      <c r="BI3" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="AZ3" s="7" t="s">
+      <c r="BJ3" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="BA3" s="7" t="s">
+      <c r="BK3" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="BB3" s="7" t="s">
+      <c r="BL3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="BC3" s="7" t="s">
+      <c r="BM3" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="BD3" s="7" t="s">
+      <c r="BN3" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="BE3" s="7" t="s">
+      <c r="BO3" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="BF3" s="7" t="s">
+      <c r="BP3" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="BG3" s="7" t="s">
+      <c r="BQ3" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="BH3" s="7" t="s">
+      <c r="BR3" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="BI3" s="7" t="s">
+      <c r="BS3" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="BJ3" s="7" t="s">
+      <c r="BT3" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="BK3" s="7" t="s">
+      <c r="BU3" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="BL3" s="7" t="s">
+      <c r="BV3" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="BM3" s="7" t="s">
+      <c r="BW3" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="BN3" s="7" t="s">
+      <c r="BX3" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="BO3" s="7" t="s">
+      <c r="BY3" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="BP3" s="7" t="s">
+      <c r="BZ3" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="BQ3" s="7" t="s">
+      <c r="CA3" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="BR3" s="7" t="s">
+      <c r="CB3" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="BS3" s="7" t="s">
+      <c r="CC3" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="BT3" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="BU3" s="7" t="s">
-        <v>210</v>
-      </c>
     </row>
-    <row r="4" spans="1:73" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:81" s="1" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>130</v>
       </c>
@@ -1808,7 +1940,7 @@
         <v>48</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y4" s="9" t="s">
         <v>9</v>
@@ -1820,7 +1952,7 @@
         <v>59</v>
       </c>
       <c r="AB4" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AC4" s="9" t="s">
         <v>47</v>
@@ -1841,13 +1973,13 @@
         <v>44</v>
       </c>
       <c r="AI4" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AJ4" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AK4" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AL4" s="9" t="s">
         <v>11</v>
@@ -1856,120 +1988,144 @@
         <v>12</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="AO4" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="AP4" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR4" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS4" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="AU4" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="AV4" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AW4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="AP4" s="9" t="s">
+      <c r="AX4" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="AQ4" s="9" t="s">
+      <c r="AY4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="AR4" s="9" t="s">
+      <c r="AZ4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="AS4" s="9" t="s">
+      <c r="BA4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="AT4" s="9" t="s">
+      <c r="BB4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AU4" s="9" t="s">
+      <c r="BC4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="AV4" s="9" t="s">
+      <c r="BD4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AW4" s="9" t="s">
+      <c r="BE4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AX4" s="9" t="s">
+      <c r="BF4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AY4" s="9" t="s">
+      <c r="BG4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AZ4" s="9" t="s">
+      <c r="BH4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BA4" s="9" t="s">
+      <c r="BI4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BB4" s="9" t="s">
+      <c r="BJ4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BC4" s="9" t="s">
+      <c r="BK4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BD4" s="9" t="s">
+      <c r="BL4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BE4" s="9" t="s">
+      <c r="BM4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="BF4" s="9" t="s">
+      <c r="BN4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="BG4" s="9" t="s">
+      <c r="BO4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="BH4" s="9" t="s">
+      <c r="BP4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="BI4" s="9" t="s">
+      <c r="BQ4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="BJ4" s="9" t="s">
+      <c r="BR4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="BK4" s="9" t="s">
+      <c r="BS4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="BL4" s="9" t="s">
+      <c r="BT4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BM4" s="9" t="s">
+      <c r="BU4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="BN4" s="9" t="s">
+      <c r="BV4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="BO4" s="9" t="s">
+      <c r="BW4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="BP4" s="9" t="s">
+      <c r="BX4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="BQ4" s="9" t="s">
+      <c r="BY4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="BR4" s="9" t="s">
+      <c r="BZ4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="BS4" s="9" t="s">
+      <c r="CA4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="BT4" s="9" t="s">
+      <c r="CB4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="BU4" s="11" t="s">
+      <c r="CC4" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:81" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BU4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:CC4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
